--- a/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
+++ b/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sistema-erp-agarcorp\storage\app\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SISTEMA-OFICIAL-AGARCORP\storage\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69A8FF0-6AA1-4116-9483-53201C04FEBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7559D6-3BA5-4768-A3DD-8FF067EBB235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
   </bookViews>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="52">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -352,6 +352,9 @@
   </si>
   <si>
     <t>Firma: {{firma_receptor}}</t>
+  </si>
+  <si>
+    <t>{{fecha}}</t>
   </si>
 </sst>
 </file>
@@ -1097,6 +1100,138 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
@@ -1115,12 +1250,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1198,138 +1327,8 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1770,60 +1769,60 @@
     <row r="1" spans="3:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="104"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="107" t="s">
+      <c r="C3" s="57"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="107"/>
-      <c r="G3" s="107"/>
-      <c r="H3" s="107"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="108"/>
-      <c r="K3" s="113" t="s">
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="114"/>
+      <c r="L3" s="67"/>
     </row>
     <row r="4" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="105"/>
-      <c r="D4" s="94"/>
-      <c r="E4" s="109"/>
-      <c r="F4" s="109"/>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="115" t="s">
+      <c r="C4" s="58"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="68" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="116"/>
+      <c r="L4" s="69"/>
     </row>
     <row r="5" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="105"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="115"/>
-      <c r="L5" s="116"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="46"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="69"/>
     </row>
     <row r="6" spans="3:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="106"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="111"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="117" t="s">
+      <c r="C6" s="59"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="70" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="118"/>
+      <c r="L6" s="71"/>
     </row>
     <row r="7" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="30"/>
@@ -1864,8 +1863,10 @@
       <c r="J9" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="K9" s="50"/>
-      <c r="L9" s="51"/>
+      <c r="K9" s="118" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="117"/>
     </row>
     <row r="10" spans="3:13" ht="23.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="22"/>
@@ -1921,33 +1922,33 @@
       <c r="M13" s="2"/>
     </row>
     <row r="14" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="55"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="55"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="60" t="s">
+      <c r="E14" s="95"/>
+      <c r="F14" s="95"/>
+      <c r="G14" s="95"/>
+      <c r="H14" s="96"/>
+      <c r="I14" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="62" t="s">
+      <c r="J14" s="102" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="63"/>
-      <c r="L14" s="64"/>
+      <c r="K14" s="103"/>
+      <c r="L14" s="104"/>
     </row>
     <row r="15" spans="3:13" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="53"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="61"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="98"/>
+      <c r="F15" s="98"/>
+      <c r="G15" s="98"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="101"/>
       <c r="J15" s="20" t="s">
         <v>8</v>
       </c>
@@ -2340,15 +2341,15 @@
       <c r="L32" s="9"/>
     </row>
     <row r="33" spans="3:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="75" t="s">
+      <c r="C33" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="D33" s="76"/>
-      <c r="E33" s="76"/>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-      <c r="I33" s="76"/>
+      <c r="D33" s="116"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="116"/>
+      <c r="G33" s="116"/>
+      <c r="H33" s="116"/>
+      <c r="I33" s="116"/>
       <c r="L33" s="8"/>
     </row>
     <row r="34" spans="3:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2362,11 +2363,11 @@
       <c r="L34" s="8"/>
     </row>
     <row r="35" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="65" t="s">
+      <c r="C35" s="105" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="66"/>
-      <c r="E35" s="66"/>
+      <c r="D35" s="106"/>
+      <c r="E35" s="106"/>
       <c r="F35" s="77" t="s">
         <v>20</v>
       </c>
@@ -2376,25 +2377,25 @@
       <c r="L35" s="8"/>
     </row>
     <row r="36" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="65" t="s">
+      <c r="C36" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="66"/>
-      <c r="E36" s="66"/>
-      <c r="F36" s="67" t="s">
+      <c r="D36" s="106"/>
+      <c r="E36" s="106"/>
+      <c r="F36" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="67"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="67"/>
-      <c r="J36" s="67"/>
-      <c r="K36" s="67"/>
-      <c r="L36" s="68"/>
+      <c r="G36" s="107"/>
+      <c r="H36" s="107"/>
+      <c r="I36" s="107"/>
+      <c r="J36" s="107"/>
+      <c r="K36" s="107"/>
+      <c r="L36" s="108"/>
     </row>
     <row r="37" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="65"/>
-      <c r="D37" s="66"/>
-      <c r="E37" s="66"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="106"/>
+      <c r="E37" s="106"/>
       <c r="F37" s="78" t="s">
         <v>22</v>
       </c>
@@ -2409,15 +2410,15 @@
       <c r="C38" s="80"/>
       <c r="D38" s="81"/>
       <c r="E38" s="81"/>
-      <c r="F38" s="91" t="s">
+      <c r="F38" s="85" t="s">
         <v>46</v>
       </c>
-      <c r="G38" s="91"/>
-      <c r="H38" s="91"/>
-      <c r="I38" s="91"/>
-      <c r="J38" s="91"/>
-      <c r="K38" s="91"/>
-      <c r="L38" s="92"/>
+      <c r="G38" s="85"/>
+      <c r="H38" s="85"/>
+      <c r="I38" s="85"/>
+      <c r="J38" s="85"/>
+      <c r="K38" s="85"/>
+      <c r="L38" s="86"/>
     </row>
     <row r="39" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="7"/>
@@ -2445,112 +2446,112 @@
       <c r="N40" s="3"/>
     </row>
     <row r="41" spans="3:14" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="82" t="s">
+      <c r="C41" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="84"/>
-      <c r="H41" s="85" t="s">
+      <c r="D41" s="55"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="82" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="86"/>
-      <c r="J41" s="86"/>
-      <c r="K41" s="86"/>
-      <c r="L41" s="87"/>
+      <c r="I41" s="83"/>
+      <c r="J41" s="83"/>
+      <c r="K41" s="83"/>
+      <c r="L41" s="84"/>
     </row>
     <row r="42" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C42" s="82" t="s">
+      <c r="C42" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="84"/>
-      <c r="H42" s="102" t="s">
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="103"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="56"/>
     </row>
     <row r="43" spans="3:14" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C43" s="88" t="s">
+      <c r="C43" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="89"/>
-      <c r="E43" s="90"/>
-      <c r="F43" s="88" t="s">
+      <c r="D43" s="73"/>
+      <c r="E43" s="74"/>
+      <c r="F43" s="72" t="s">
         <v>34</v>
       </c>
-      <c r="G43" s="90"/>
-      <c r="H43" s="88" t="s">
+      <c r="G43" s="74"/>
+      <c r="H43" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="I43" s="90"/>
-      <c r="J43" s="88" t="s">
+      <c r="I43" s="74"/>
+      <c r="J43" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="K43" s="89"/>
-      <c r="L43" s="90"/>
+      <c r="K43" s="73"/>
+      <c r="L43" s="74"/>
       <c r="N43" s="3"/>
     </row>
     <row r="44" spans="3:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="96" t="s">
+      <c r="C44" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="D44" s="97"/>
-      <c r="E44" s="98"/>
-      <c r="F44" s="96" t="s">
+      <c r="D44" s="49"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="G44" s="98"/>
-      <c r="H44" s="96" t="s">
+      <c r="G44" s="50"/>
+      <c r="H44" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="I44" s="98"/>
-      <c r="J44" s="99" t="s">
+      <c r="I44" s="50"/>
+      <c r="J44" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="K44" s="100"/>
-      <c r="L44" s="101"/>
+      <c r="K44" s="52"/>
+      <c r="L44" s="53"/>
     </row>
     <row r="45" spans="3:14" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="69" t="s">
+      <c r="C45" s="109" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="74"/>
-      <c r="E45" s="70"/>
-      <c r="F45" s="69" t="s">
+      <c r="D45" s="114"/>
+      <c r="E45" s="110"/>
+      <c r="F45" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="G45" s="70"/>
-      <c r="H45" s="69" t="s">
+      <c r="G45" s="110"/>
+      <c r="H45" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="I45" s="70"/>
-      <c r="J45" s="71" t="s">
+      <c r="I45" s="110"/>
+      <c r="J45" s="111" t="s">
         <v>50</v>
       </c>
-      <c r="K45" s="72"/>
-      <c r="L45" s="73"/>
+      <c r="K45" s="112"/>
+      <c r="L45" s="113"/>
     </row>
     <row r="46" spans="3:14" ht="24.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C46" s="45" t="s">
+      <c r="C46" s="87" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="46"/>
-      <c r="E46" s="47"/>
-      <c r="F46" s="48" t="s">
+      <c r="D46" s="88"/>
+      <c r="E46" s="89"/>
+      <c r="F46" s="90" t="s">
         <v>41</v>
       </c>
-      <c r="G46" s="49"/>
-      <c r="H46" s="48" t="s">
+      <c r="G46" s="91"/>
+      <c r="H46" s="90" t="s">
         <v>42</v>
       </c>
-      <c r="I46" s="49"/>
+      <c r="I46" s="91"/>
       <c r="J46" s="38" t="s">
         <v>43</v>
       </c>
@@ -2598,7 +2599,29 @@
     <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="38">
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="C36:E37"/>
+    <mergeCell ref="F36:L36"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="J45:L45"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="F37:L37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="H41:L41"/>
+    <mergeCell ref="F38:L38"/>
     <mergeCell ref="D3:D6"/>
     <mergeCell ref="C44:E44"/>
     <mergeCell ref="F44:G44"/>
@@ -2615,29 +2638,6 @@
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F37:L37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:L41"/>
-    <mergeCell ref="F38:L38"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="C36:E37"/>
-    <mergeCell ref="F36:L36"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="C35:E35"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>

--- a/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
+++ b/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SISTEMA-OFICIAL-AGARCORP\storage\app\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xavier\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E7559D6-3BA5-4768-A3DD-8FF067EBB235}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABACF0F4-D4C9-4884-A184-64D4DE9D5848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO SIN FORMULA" sheetId="2" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="54">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -207,9 +207,6 @@
   </si>
   <si>
     <t>Solicitado por: {{solicitado_por}}</t>
-  </si>
-  <si>
-    <t>Cargo: {{cargo_solicitante}}</t>
   </si>
   <si>
     <t>Por almacen: {{por_almacen}}</t>
@@ -342,19 +339,28 @@
     <t>{{para_uso_linea3}}</t>
   </si>
   <si>
-    <t>Firma: {{firma_solicitante}}</t>
-  </si>
-  <si>
-    <t>Firma: {{firma_almacen}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Firma: {{firma_aprobador}}    </t>
-  </si>
-  <si>
-    <t>Firma: {{firma_receptor}}</t>
-  </si>
-  <si>
     <t>{{fecha}}</t>
+  </si>
+  <si>
+    <t>Firma:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cargo: {{cargo_solicitante}} </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {{firma_solicitante}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firma: </t>
+  </si>
+  <si>
+    <t>{{firma_almacen}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{firma_aprobador}}    </t>
+  </si>
+  <si>
+    <t>{{firma_receptor}}</t>
   </si>
 </sst>
 </file>
@@ -1100,6 +1106,166 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1109,30 +1275,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1190,145 +1335,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1395,15 +1401,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>106680</xdr:colOff>
+          <xdr:colOff>104775</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>129540</xdr:rowOff>
+          <xdr:rowOff>133350</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>480060</xdr:colOff>
+          <xdr:colOff>476250</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>129540</xdr:rowOff>
+          <xdr:rowOff>133350</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1448,9 +1454,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1488,7 +1494,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1594,7 +1600,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1736,7 +1742,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1748,83 +1754,83 @@
     <tabColor indexed="52"/>
   </sheetPr>
   <dimension ref="C1:N74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
     <col min="6" max="6" width="23" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.77734375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.109375" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.44140625" style="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.7109375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.140625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="57"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="60" t="s">
+    <row r="1" spans="3:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="3:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="101"/>
+      <c r="D3" s="96"/>
+      <c r="E3" s="104" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="66" t="s">
+      <c r="F3" s="104"/>
+      <c r="G3" s="104"/>
+      <c r="H3" s="104"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="110" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="67"/>
-    </row>
-    <row r="4" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="58"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="68" t="s">
+      <c r="L3" s="111"/>
+    </row>
+    <row r="4" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="102"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="112" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="69"/>
-    </row>
-    <row r="5" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="58"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="69"/>
-    </row>
-    <row r="6" spans="3:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="59"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="70" t="s">
+      <c r="L4" s="113"/>
+    </row>
+    <row r="5" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="102"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="106"/>
+      <c r="G5" s="106"/>
+      <c r="H5" s="106"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="112"/>
+      <c r="L5" s="113"/>
+    </row>
+    <row r="6" spans="3:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="103"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="108"/>
+      <c r="G6" s="108"/>
+      <c r="H6" s="108"/>
+      <c r="I6" s="108"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="114" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="71"/>
-    </row>
-    <row r="7" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L6" s="115"/>
+    </row>
+    <row r="7" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="30"/>
       <c r="D7" s="28"/>
       <c r="E7" s="29"/>
@@ -1836,7 +1842,7 @@
       <c r="K7" s="28"/>
       <c r="L7" s="27"/>
     </row>
-    <row r="8" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="30"/>
       <c r="D8" s="28"/>
       <c r="E8" s="29"/>
@@ -1848,7 +1854,7 @@
       <c r="K8" s="28"/>
       <c r="L8" s="27"/>
     </row>
-    <row r="9" spans="3:13" ht="23.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:13" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="22"/>
       <c r="D9" s="2"/>
       <c r="E9" s="25" t="s">
@@ -1863,12 +1869,12 @@
       <c r="J9" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="K9" s="118" t="s">
-        <v>51</v>
-      </c>
-      <c r="L9" s="117"/>
-    </row>
-    <row r="10" spans="3:13" ht="23.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K9" s="46" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="45"/>
+    </row>
+    <row r="10" spans="3:13" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="22"/>
       <c r="D10" s="2"/>
       <c r="E10" s="25" t="s">
@@ -1884,7 +1890,7 @@
       <c r="K10" s="24"/>
       <c r="L10" s="23"/>
     </row>
-    <row r="11" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="22"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -1896,7 +1902,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="23"/>
     </row>
-    <row r="12" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="22"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1908,7 +1914,7 @@
       <c r="K12" s="24"/>
       <c r="L12" s="23"/>
     </row>
-    <row r="13" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="22"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1921,34 +1927,34 @@
       <c r="L13" s="21"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="92" t="s">
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
+      <c r="C14" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="94" t="s">
+      <c r="D14" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="96"/>
-      <c r="I14" s="100" t="s">
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="102" t="s">
+      <c r="J14" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="103"/>
-      <c r="L14" s="104"/>
-    </row>
-    <row r="15" spans="3:13" ht="17.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="93"/>
-      <c r="D15" s="97"/>
-      <c r="E15" s="98"/>
-      <c r="F15" s="98"/>
-      <c r="G15" s="98"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="101"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="70"/>
+    </row>
+    <row r="15" spans="3:13" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="57"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="65"/>
       <c r="J15" s="20" t="s">
         <v>8</v>
       </c>
@@ -1959,12 +1965,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" s="33"/>
       <c r="F16" s="33"/>
@@ -1983,12 +1989,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="3:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" s="18"/>
       <c r="F17" s="18"/>
@@ -2007,12 +2013,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E18" s="18"/>
       <c r="F18" s="18"/>
@@ -2031,12 +2037,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E19" s="18"/>
       <c r="F19" s="18"/>
@@ -2055,12 +2061,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E20" s="18"/>
       <c r="F20" s="18"/>
@@ -2079,12 +2085,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" s="18"/>
       <c r="F21" s="18"/>
@@ -2103,12 +2109,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D22" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="18"/>
@@ -2127,12 +2133,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D23" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I23" s="35" t="s">
         <v>28</v>
@@ -2147,12 +2153,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D24" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E24" s="40"/>
       <c r="F24" s="40"/>
@@ -2171,12 +2177,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E25" s="33"/>
       <c r="F25" s="33"/>
@@ -2195,12 +2201,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E26" s="33"/>
       <c r="F26" s="33"/>
@@ -2219,12 +2225,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" s="33"/>
       <c r="F27" s="33"/>
@@ -2243,12 +2249,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E28" s="33"/>
       <c r="F28" s="33"/>
@@ -2267,12 +2273,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D29" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E29" s="33"/>
       <c r="F29" s="33"/>
@@ -2291,12 +2297,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="16" t="s">
         <v>27</v>
       </c>
       <c r="D30" s="32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" s="33"/>
       <c r="F30" s="33"/>
@@ -2316,7 +2322,7 @@
       </c>
       <c r="N30" s="31"/>
     </row>
-    <row r="31" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="12"/>
       <c r="D31" s="11"/>
       <c r="E31" s="5"/>
@@ -2328,7 +2334,7 @@
       <c r="K31" s="10"/>
       <c r="L31" s="9"/>
     </row>
-    <row r="32" spans="3:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="12"/>
       <c r="D32" s="11"/>
       <c r="E32" s="5"/>
@@ -2340,19 +2346,19 @@
       <c r="K32" s="10"/>
       <c r="L32" s="9"/>
     </row>
-    <row r="33" spans="3:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="115" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="116"/>
-      <c r="E33" s="116"/>
-      <c r="F33" s="116"/>
-      <c r="G33" s="116"/>
-      <c r="H33" s="116"/>
-      <c r="I33" s="116"/>
+    <row r="33" spans="3:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="81" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="82"/>
+      <c r="E33" s="82"/>
+      <c r="F33" s="82"/>
+      <c r="G33" s="82"/>
+      <c r="H33" s="82"/>
+      <c r="I33" s="82"/>
       <c r="L33" s="8"/>
     </row>
-    <row r="34" spans="3:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="36"/>
       <c r="D34" s="37"/>
       <c r="E34" s="37"/>
@@ -2362,65 +2368,65 @@
       <c r="I34" s="37"/>
       <c r="L34" s="8"/>
     </row>
-    <row r="35" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="105" t="s">
+    <row r="35" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="106"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="77" t="s">
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="G35" s="77"/>
+      <c r="G35" s="86"/>
       <c r="H35" s="37"/>
       <c r="I35" s="37"/>
       <c r="L35" s="8"/>
     </row>
-    <row r="36" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="105" t="s">
+    <row r="36" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="106"/>
-      <c r="E36" s="106"/>
-      <c r="F36" s="107" t="s">
+      <c r="D36" s="72"/>
+      <c r="E36" s="72"/>
+      <c r="F36" s="73" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="107"/>
-      <c r="H36" s="107"/>
-      <c r="I36" s="107"/>
-      <c r="J36" s="107"/>
-      <c r="K36" s="107"/>
-      <c r="L36" s="108"/>
-    </row>
-    <row r="37" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="105"/>
-      <c r="D37" s="106"/>
-      <c r="E37" s="106"/>
-      <c r="F37" s="78" t="s">
+      <c r="G36" s="73"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73"/>
+      <c r="J36" s="73"/>
+      <c r="K36" s="73"/>
+      <c r="L36" s="74"/>
+    </row>
+    <row r="37" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="71"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="72"/>
+      <c r="F37" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="78"/>
-      <c r="H37" s="78"/>
-      <c r="I37" s="78"/>
-      <c r="J37" s="78"/>
-      <c r="K37" s="78"/>
-      <c r="L37" s="79"/>
-    </row>
-    <row r="38" spans="3:14" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="80"/>
-      <c r="D38" s="81"/>
-      <c r="E38" s="81"/>
-      <c r="F38" s="85" t="s">
-        <v>46</v>
-      </c>
-      <c r="G38" s="85"/>
-      <c r="H38" s="85"/>
-      <c r="I38" s="85"/>
-      <c r="J38" s="85"/>
-      <c r="K38" s="85"/>
-      <c r="L38" s="86"/>
-    </row>
-    <row r="39" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G37" s="87"/>
+      <c r="H37" s="87"/>
+      <c r="I37" s="87"/>
+      <c r="J37" s="87"/>
+      <c r="K37" s="87"/>
+      <c r="L37" s="88"/>
+    </row>
+    <row r="38" spans="3:14" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="89"/>
+      <c r="D38" s="90"/>
+      <c r="E38" s="90"/>
+      <c r="F38" s="94" t="s">
+        <v>45</v>
+      </c>
+      <c r="G38" s="94"/>
+      <c r="H38" s="94"/>
+      <c r="I38" s="94"/>
+      <c r="J38" s="94"/>
+      <c r="K38" s="94"/>
+      <c r="L38" s="95"/>
+    </row>
+    <row r="39" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="7"/>
       <c r="D39" s="6"/>
       <c r="E39" s="2"/>
@@ -2432,7 +2438,7 @@
       <c r="K39" s="5"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="3:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="3:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C40" s="7"/>
       <c r="D40" s="6"/>
       <c r="E40" s="2"/>
@@ -2445,122 +2451,130 @@
       <c r="L40" s="4"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="3:14" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="75" t="s">
+    <row r="41" spans="3:14" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="55"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="82" t="s">
+      <c r="D41" s="84"/>
+      <c r="E41" s="84"/>
+      <c r="F41" s="84"/>
+      <c r="G41" s="85"/>
+      <c r="H41" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="84"/>
-    </row>
-    <row r="42" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C42" s="75" t="s">
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="93"/>
+    </row>
+    <row r="42" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="83" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-      <c r="F42" s="55"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="54" t="s">
+      <c r="D42" s="84"/>
+      <c r="E42" s="84"/>
+      <c r="F42" s="84"/>
+      <c r="G42" s="85"/>
+      <c r="H42" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="I42" s="55"/>
-      <c r="J42" s="55"/>
-      <c r="K42" s="55"/>
-      <c r="L42" s="56"/>
-    </row>
-    <row r="43" spans="3:14" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C43" s="72" t="s">
+      <c r="I42" s="84"/>
+      <c r="J42" s="84"/>
+      <c r="K42" s="84"/>
+      <c r="L42" s="100"/>
+    </row>
+    <row r="43" spans="3:14" ht="40.15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="116" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="73"/>
-      <c r="E43" s="74"/>
-      <c r="F43" s="72" t="s">
+      <c r="D43" s="117"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="116" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="118"/>
+      <c r="H43" s="116" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43" s="118"/>
+      <c r="J43" s="116" t="s">
+        <v>36</v>
+      </c>
+      <c r="K43" s="117"/>
+      <c r="L43" s="118"/>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="3:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="D44" s="67"/>
+      <c r="E44" s="47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F44" s="48" t="s">
         <v>34</v>
       </c>
-      <c r="G43" s="74"/>
-      <c r="H43" s="72" t="s">
-        <v>36</v>
-      </c>
-      <c r="I43" s="74"/>
-      <c r="J43" s="72" t="s">
+      <c r="G44" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="H44" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="K43" s="73"/>
-      <c r="L43" s="74"/>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="3:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="48" t="s">
-        <v>33</v>
-      </c>
-      <c r="D44" s="49"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G44" s="50"/>
-      <c r="H44" s="48" t="s">
+      <c r="I44" s="50" t="s">
+        <v>52</v>
+      </c>
+      <c r="J44" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="I44" s="50"/>
-      <c r="J44" s="51" t="s">
+      <c r="K44" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="L44" s="50"/>
+    </row>
+    <row r="45" spans="3:14" ht="24.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="75" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="80"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="G45" s="76"/>
+      <c r="H45" s="75" t="s">
+        <v>50</v>
+      </c>
+      <c r="I45" s="76"/>
+      <c r="J45" s="77" t="s">
+        <v>50</v>
+      </c>
+      <c r="K45" s="78"/>
+      <c r="L45" s="79"/>
+    </row>
+    <row r="46" spans="3:14" ht="24.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="K44" s="52"/>
-      <c r="L44" s="53"/>
-    </row>
-    <row r="45" spans="3:14" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="109" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="114"/>
-      <c r="E45" s="110"/>
-      <c r="F45" s="109" t="s">
-        <v>48</v>
-      </c>
-      <c r="G45" s="110"/>
-      <c r="H45" s="109" t="s">
-        <v>49</v>
-      </c>
-      <c r="I45" s="110"/>
-      <c r="J45" s="111" t="s">
-        <v>50</v>
-      </c>
-      <c r="K45" s="112"/>
-      <c r="L45" s="113"/>
-    </row>
-    <row r="46" spans="3:14" ht="24.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C46" s="87" t="s">
+      <c r="D46" s="52"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="D46" s="88"/>
-      <c r="E46" s="89"/>
-      <c r="F46" s="90" t="s">
+      <c r="G46" s="55"/>
+      <c r="H46" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="G46" s="91"/>
-      <c r="H46" s="90" t="s">
+      <c r="I46" s="55"/>
+      <c r="J46" s="38" t="s">
         <v>42</v>
-      </c>
-      <c r="I46" s="91"/>
-      <c r="J46" s="38" t="s">
-        <v>43</v>
       </c>
       <c r="K46" s="39"/>
       <c r="L46" s="42" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -2572,40 +2586,46 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="M49" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="50" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:H15"/>
-    <mergeCell ref="I14:I15"/>
+  <mergeCells count="35">
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="E3:J6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="H42:L42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="J43:L43"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="C36:E37"/>
     <mergeCell ref="F36:L36"/>
@@ -2622,22 +2642,13 @@
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="H41:L41"/>
     <mergeCell ref="F38:L38"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="H42:L42"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="E3:J6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="C44:D44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
@@ -2653,15 +2664,15 @@
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>106680</xdr:colOff>
+                <xdr:colOff>104775</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>129540</xdr:rowOff>
+                <xdr:rowOff>133350</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>480060</xdr:colOff>
+                <xdr:colOff>476250</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>129540</xdr:rowOff>
+                <xdr:rowOff>133350</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -2678,7 +2689,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF103C6C-43B0-44D4-BD77-E1E3ABD37B7E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
+++ b/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Xavier\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SISTEMA-OFICIAL-AGARCORP\storage\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABACF0F4-D4C9-4884-A184-64D4DE9D5848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A015A1-AD0D-459B-8C34-5038D2465E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO SIN FORMULA" sheetId="2" r:id="rId1"/>
@@ -1120,6 +1120,167 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1"/>
       <protection locked="0"/>
@@ -1172,167 +1333,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1355,61 +1355,20 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>168218</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>173234</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="722480" cy="645734"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="2530418" y="17546834"/>
-          <a:ext cx="722480" cy="645734"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>104775</xdr:colOff>
+          <xdr:colOff>106680</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>133350</xdr:rowOff>
+          <xdr:rowOff>137160</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>133350</xdr:rowOff>
+          <xdr:rowOff>137160</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1450,13 +1409,74 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>160400</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>185054</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1011313</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>104499</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10FA9D5A-E4CC-4060-8F3D-6DD1F8E6BA96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="2522600" y="838197"/>
+          <a:ext cx="850913" cy="692331"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1494,7 +1514,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1600,7 +1620,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1742,7 +1762,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1754,83 +1774,83 @@
     <tabColor indexed="52"/>
   </sheetPr>
   <dimension ref="C1:N74"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="23" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.140625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="24.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.88671875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="21.109375" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="3:13" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="101"/>
-      <c r="D3" s="96"/>
-      <c r="E3" s="104" t="s">
+    <row r="1" spans="3:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="51"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="104"/>
-      <c r="G3" s="104"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="104"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="110" t="s">
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="111"/>
-    </row>
-    <row r="4" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="102"/>
-      <c r="D4" s="97"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="112" t="s">
+      <c r="L3" s="61"/>
+    </row>
+    <row r="4" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="52"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="57"/>
+      <c r="K4" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="L4" s="113"/>
-    </row>
-    <row r="5" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="102"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="106"/>
-      <c r="F5" s="106"/>
-      <c r="G5" s="106"/>
-      <c r="H5" s="106"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="112"/>
-      <c r="L5" s="113"/>
-    </row>
-    <row r="6" spans="3:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="103"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="108"/>
-      <c r="G6" s="108"/>
-      <c r="H6" s="108"/>
-      <c r="I6" s="108"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="114" t="s">
+      <c r="L4" s="63"/>
+    </row>
+    <row r="5" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="52"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="56"/>
+      <c r="F5" s="56"/>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="62"/>
+      <c r="L5" s="63"/>
+    </row>
+    <row r="6" spans="3:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="53"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="59"/>
+      <c r="K6" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="115"/>
-    </row>
-    <row r="7" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L6" s="65"/>
+    </row>
+    <row r="7" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="30"/>
       <c r="D7" s="28"/>
       <c r="E7" s="29"/>
@@ -1842,7 +1862,7 @@
       <c r="K7" s="28"/>
       <c r="L7" s="27"/>
     </row>
-    <row r="8" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="30"/>
       <c r="D8" s="28"/>
       <c r="E8" s="29"/>
@@ -1854,7 +1874,7 @@
       <c r="K8" s="28"/>
       <c r="L8" s="27"/>
     </row>
-    <row r="9" spans="3:13" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="22"/>
       <c r="D9" s="2"/>
       <c r="E9" s="25" t="s">
@@ -1874,8 +1894,8 @@
       </c>
       <c r="L9" s="45"/>
     </row>
-    <row r="10" spans="3:13" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C10" s="22"/>
+    <row r="10" spans="3:13" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C10"/>
       <c r="D10" s="2"/>
       <c r="E10" s="25" t="s">
         <v>12</v>
@@ -1890,7 +1910,7 @@
       <c r="K10" s="24"/>
       <c r="L10" s="23"/>
     </row>
-    <row r="11" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="22"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -1902,7 +1922,7 @@
       <c r="K11" s="24"/>
       <c r="L11" s="23"/>
     </row>
-    <row r="12" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="22"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1914,7 +1934,7 @@
       <c r="K12" s="24"/>
       <c r="L12" s="23"/>
     </row>
-    <row r="13" spans="3:13" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="22"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1927,34 +1947,34 @@
       <c r="L13" s="21"/>
       <c r="M13" s="2"/>
     </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C14" s="56" t="s">
+    <row r="14" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C14" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="59"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
-      <c r="H14" s="60"/>
-      <c r="I14" s="64" t="s">
+      <c r="E14" s="110"/>
+      <c r="F14" s="110"/>
+      <c r="G14" s="110"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="J14" s="68" t="s">
+      <c r="J14" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="69"/>
-      <c r="L14" s="70"/>
-    </row>
-    <row r="15" spans="3:13" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="57"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="65"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="77"/>
+    </row>
+    <row r="15" spans="3:13" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="108"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="113"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="116"/>
       <c r="J15" s="20" t="s">
         <v>8</v>
       </c>
@@ -1965,7 +1985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="16" t="s">
         <v>27</v>
       </c>
@@ -1989,7 +2009,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="3:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="16" t="s">
         <v>27</v>
       </c>
@@ -2013,7 +2033,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="16" t="s">
         <v>27</v>
       </c>
@@ -2037,7 +2057,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="16" t="s">
         <v>27</v>
       </c>
@@ -2061,7 +2081,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="16" t="s">
         <v>27</v>
       </c>
@@ -2085,7 +2105,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="16" t="s">
         <v>27</v>
       </c>
@@ -2109,7 +2129,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="16" t="s">
         <v>27</v>
       </c>
@@ -2133,7 +2153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="16" t="s">
         <v>27</v>
       </c>
@@ -2153,7 +2173,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="16" t="s">
         <v>27</v>
       </c>
@@ -2177,7 +2197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="16" t="s">
         <v>27</v>
       </c>
@@ -2201,7 +2221,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="16" t="s">
         <v>27</v>
       </c>
@@ -2225,7 +2245,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="16" t="s">
         <v>27</v>
       </c>
@@ -2249,7 +2269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="16" t="s">
         <v>27</v>
       </c>
@@ -2273,7 +2293,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="16" t="s">
         <v>27</v>
       </c>
@@ -2297,7 +2317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="16" t="s">
         <v>27</v>
       </c>
@@ -2322,7 +2342,7 @@
       </c>
       <c r="N30" s="31"/>
     </row>
-    <row r="31" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="12"/>
       <c r="D31" s="11"/>
       <c r="E31" s="5"/>
@@ -2334,7 +2354,7 @@
       <c r="K31" s="10"/>
       <c r="L31" s="9"/>
     </row>
-    <row r="32" spans="3:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="12"/>
       <c r="D32" s="11"/>
       <c r="E32" s="5"/>
@@ -2346,19 +2366,19 @@
       <c r="K32" s="10"/>
       <c r="L32" s="9"/>
     </row>
-    <row r="33" spans="3:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="81" t="s">
+    <row r="33" spans="3:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="82"/>
-      <c r="E33" s="82"/>
-      <c r="F33" s="82"/>
-      <c r="G33" s="82"/>
-      <c r="H33" s="82"/>
-      <c r="I33" s="82"/>
+      <c r="D33" s="89"/>
+      <c r="E33" s="89"/>
+      <c r="F33" s="89"/>
+      <c r="G33" s="89"/>
+      <c r="H33" s="89"/>
+      <c r="I33" s="89"/>
       <c r="L33" s="8"/>
     </row>
-    <row r="34" spans="3:14" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="36"/>
       <c r="D34" s="37"/>
       <c r="E34" s="37"/>
@@ -2368,65 +2388,65 @@
       <c r="I34" s="37"/>
       <c r="L34" s="8"/>
     </row>
-    <row r="35" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="71" t="s">
+    <row r="35" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="86" t="s">
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="G35" s="86"/>
+      <c r="G35" s="92"/>
       <c r="H35" s="37"/>
       <c r="I35" s="37"/>
       <c r="L35" s="8"/>
     </row>
-    <row r="36" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="71" t="s">
+    <row r="36" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="73" t="s">
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="80" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="73"/>
-      <c r="H36" s="73"/>
-      <c r="I36" s="73"/>
-      <c r="J36" s="73"/>
-      <c r="K36" s="73"/>
-      <c r="L36" s="74"/>
-    </row>
-    <row r="37" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="71"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="72"/>
-      <c r="F37" s="87" t="s">
+      <c r="G36" s="80"/>
+      <c r="H36" s="80"/>
+      <c r="I36" s="80"/>
+      <c r="J36" s="80"/>
+      <c r="K36" s="80"/>
+      <c r="L36" s="81"/>
+    </row>
+    <row r="37" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="78"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="G37" s="87"/>
-      <c r="H37" s="87"/>
-      <c r="I37" s="87"/>
-      <c r="J37" s="87"/>
-      <c r="K37" s="87"/>
-      <c r="L37" s="88"/>
-    </row>
-    <row r="38" spans="3:14" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="89"/>
-      <c r="D38" s="90"/>
-      <c r="E38" s="90"/>
-      <c r="F38" s="94" t="s">
+      <c r="G37" s="93"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="93"/>
+      <c r="J37" s="93"/>
+      <c r="K37" s="93"/>
+      <c r="L37" s="94"/>
+    </row>
+    <row r="38" spans="3:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="95"/>
+      <c r="D38" s="96"/>
+      <c r="E38" s="96"/>
+      <c r="F38" s="100" t="s">
         <v>45</v>
       </c>
-      <c r="G38" s="94"/>
-      <c r="H38" s="94"/>
-      <c r="I38" s="94"/>
-      <c r="J38" s="94"/>
-      <c r="K38" s="94"/>
-      <c r="L38" s="95"/>
-    </row>
-    <row r="39" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G38" s="100"/>
+      <c r="H38" s="100"/>
+      <c r="I38" s="100"/>
+      <c r="J38" s="100"/>
+      <c r="K38" s="100"/>
+      <c r="L38" s="101"/>
+    </row>
+    <row r="39" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="7"/>
       <c r="D39" s="6"/>
       <c r="E39" s="2"/>
@@ -2438,7 +2458,7 @@
       <c r="K39" s="5"/>
       <c r="L39" s="4"/>
     </row>
-    <row r="40" spans="3:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="3:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C40" s="7"/>
       <c r="D40" s="6"/>
       <c r="E40" s="2"/>
@@ -2451,64 +2471,64 @@
       <c r="L40" s="4"/>
       <c r="N40" s="3"/>
     </row>
-    <row r="41" spans="3:14" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="83" t="s">
+    <row r="41" spans="3:14" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="84"/>
-      <c r="E41" s="84"/>
-      <c r="F41" s="84"/>
-      <c r="G41" s="85"/>
-      <c r="H41" s="91" t="s">
+      <c r="D41" s="70"/>
+      <c r="E41" s="70"/>
+      <c r="F41" s="70"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="93"/>
-    </row>
-    <row r="42" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="83" t="s">
+      <c r="I41" s="98"/>
+      <c r="J41" s="98"/>
+      <c r="K41" s="98"/>
+      <c r="L41" s="99"/>
+    </row>
+    <row r="42" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C42" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="84"/>
-      <c r="E42" s="84"/>
-      <c r="F42" s="84"/>
-      <c r="G42" s="85"/>
-      <c r="H42" s="99" t="s">
+      <c r="D42" s="70"/>
+      <c r="E42" s="70"/>
+      <c r="F42" s="70"/>
+      <c r="G42" s="91"/>
+      <c r="H42" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="I42" s="84"/>
-      <c r="J42" s="84"/>
-      <c r="K42" s="84"/>
-      <c r="L42" s="100"/>
-    </row>
-    <row r="43" spans="3:14" ht="40.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C43" s="116" t="s">
+      <c r="I42" s="70"/>
+      <c r="J42" s="70"/>
+      <c r="K42" s="70"/>
+      <c r="L42" s="71"/>
+    </row>
+    <row r="43" spans="3:14" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C43" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="117"/>
-      <c r="E43" s="118"/>
-      <c r="F43" s="116" t="s">
+      <c r="D43" s="73"/>
+      <c r="E43" s="74"/>
+      <c r="F43" s="72" t="s">
         <v>33</v>
       </c>
-      <c r="G43" s="118"/>
-      <c r="H43" s="116" t="s">
+      <c r="G43" s="74"/>
+      <c r="H43" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="I43" s="118"/>
-      <c r="J43" s="116" t="s">
+      <c r="I43" s="74"/>
+      <c r="J43" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="K43" s="117"/>
-      <c r="L43" s="118"/>
+      <c r="K43" s="73"/>
+      <c r="L43" s="74"/>
       <c r="N43" s="3"/>
     </row>
-    <row r="44" spans="3:14" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C44" s="66" t="s">
+    <row r="44" spans="3:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="117" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="67"/>
+      <c r="D44" s="118"/>
       <c r="E44" s="47" t="s">
         <v>49</v>
       </c>
@@ -2532,40 +2552,40 @@
       </c>
       <c r="L44" s="50"/>
     </row>
-    <row r="45" spans="3:14" ht="24.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C45" s="75" t="s">
+    <row r="45" spans="3:14" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="D45" s="80"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="75" t="s">
+      <c r="D45" s="87"/>
+      <c r="E45" s="83"/>
+      <c r="F45" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="G45" s="76"/>
-      <c r="H45" s="75" t="s">
+      <c r="G45" s="83"/>
+      <c r="H45" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="I45" s="76"/>
-      <c r="J45" s="77" t="s">
+      <c r="I45" s="83"/>
+      <c r="J45" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="K45" s="78"/>
-      <c r="L45" s="79"/>
-    </row>
-    <row r="46" spans="3:14" ht="24.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="51" t="s">
+      <c r="K45" s="85"/>
+      <c r="L45" s="86"/>
+    </row>
+    <row r="46" spans="3:14" ht="24.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C46" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="52"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="54" t="s">
+      <c r="D46" s="103"/>
+      <c r="E46" s="104"/>
+      <c r="F46" s="105" t="s">
         <v>40</v>
       </c>
-      <c r="G46" s="55"/>
-      <c r="H46" s="54" t="s">
+      <c r="G46" s="106"/>
+      <c r="H46" s="105" t="s">
         <v>41</v>
       </c>
-      <c r="I46" s="55"/>
+      <c r="I46" s="106"/>
       <c r="J46" s="38" t="s">
         <v>42</v>
       </c>
@@ -2574,7 +2594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
@@ -2586,46 +2606,41 @@
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
     </row>
-    <row r="48" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="49" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M49" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="56" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="55" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="69" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="E3:J6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="H42:L42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="C44:D44"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="C36:E37"/>
     <mergeCell ref="F36:L36"/>
@@ -2642,13 +2657,18 @@
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="H41:L41"/>
     <mergeCell ref="F38:L38"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="H42:L42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="J43:L43"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="E3:J6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D3:D6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
@@ -2664,15 +2684,15 @@
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>104775</xdr:colOff>
+                <xdr:colOff>106680</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
+                <xdr:rowOff>137160</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>476250</xdr:colOff>
+                <xdr:colOff>480060</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
+                <xdr:rowOff>137160</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -2689,7 +2709,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF103C6C-43B0-44D4-BD77-E1E3ABD37B7E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
+++ b/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SISTEMA-OFICIAL-AGARCORP\storage\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89A015A1-AD0D-459B-8C34-5038D2465E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE540AF-840C-40F7-9C99-CFC96D4665E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'FORMATO SIN FORMULA'!$C$3:$L$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'FORMATO SIN FORMULA'!$C$3:$L$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,12 +66,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="53">
   <si>
     <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Hora:</t>
   </si>
   <si>
     <t>Fecha:</t>
@@ -272,9 +269,6 @@
   </si>
   <si>
     <t xml:space="preserve">Fecha: {{fecha_aprobador}}     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha: {{fecha_receptor}}              </t>
   </si>
   <si>
     <r>
@@ -339,18 +333,12 @@
     <t>{{para_uso_linea3}}</t>
   </si>
   <si>
-    <t>{{fecha}}</t>
-  </si>
-  <si>
     <t>Firma:</t>
   </si>
   <si>
     <t xml:space="preserve">Cargo: {{cargo_solicitante}} </t>
   </si>
   <si>
-    <t xml:space="preserve"> {{firma_solicitante}}</t>
-  </si>
-  <si>
     <t xml:space="preserve">Firma: </t>
   </si>
   <si>
@@ -361,13 +349,22 @@
   </si>
   <si>
     <t>{{firma_receptor}}</t>
+  </si>
+  <si>
+    <t>{{firma_solicitante}}</t>
+  </si>
+  <si>
+    <t>{{fecha_solicitante}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha: {{fecha_receptor}}    Hora: {{hora_receptor}}           </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -416,6 +413,18 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -437,7 +446,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="42">
     <border>
       <left/>
       <right/>
@@ -659,17 +668,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -684,32 +682,6 @@
     <border>
       <left/>
       <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top style="medium">
         <color indexed="64"/>
       </top>
@@ -955,11 +927,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -970,51 +946,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="119">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1032,36 +996,18 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1073,22 +1019,8 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1099,46 +1031,115 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="27" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1147,193 +1148,168 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="42" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1427,7 +1403,7 @@
         <xdr:cNvPr id="4" name="Imagen 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{10FA9D5A-E4CC-4060-8F3D-6DD1F8E6BA96}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1773,7 +1749,7 @@
   <sheetPr>
     <tabColor indexed="52"/>
   </sheetPr>
-  <dimension ref="C1:N74"/>
+  <dimension ref="C1:N75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -1795,859 +1771,892 @@
     <row r="1" spans="3:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="51"/>
+      <c r="C3" s="57"/>
       <c r="D3" s="66"/>
-      <c r="E3" s="54" t="s">
+      <c r="E3" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="60"/>
+      <c r="G3" s="60"/>
+      <c r="H3" s="60"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="91" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="92"/>
+    </row>
+    <row r="4" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="58"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="62"/>
+      <c r="H4" s="62"/>
+      <c r="I4" s="62"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="93" t="s">
+        <v>14</v>
+      </c>
+      <c r="L4" s="94"/>
+    </row>
+    <row r="5" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="58"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="62"/>
+      <c r="H5" s="62"/>
+      <c r="I5" s="62"/>
+      <c r="J5" s="63"/>
+      <c r="K5" s="93"/>
+      <c r="L5" s="94"/>
+    </row>
+    <row r="6" spans="3:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="59"/>
+      <c r="D6" s="68"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="65"/>
+      <c r="K6" s="95" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" s="96"/>
+    </row>
+    <row r="7" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="31"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="30"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="20"/>
+    </row>
+    <row r="8" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="32"/>
+      <c r="D8" s="69"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="30"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="20"/>
+    </row>
+    <row r="9" spans="3:13" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="18"/>
+      <c r="D9" s="70"/>
+      <c r="E9" s="71" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3" s="61"/>
-    </row>
-    <row r="4" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="52"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="57"/>
-      <c r="K4" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="63"/>
-    </row>
-    <row r="5" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="52"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="56"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="56"/>
-      <c r="H5" s="56"/>
-      <c r="I5" s="56"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="62"/>
-      <c r="L5" s="63"/>
-    </row>
-    <row r="6" spans="3:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="53"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="64" t="s">
-        <v>14</v>
-      </c>
-      <c r="L6" s="65"/>
-    </row>
-    <row r="7" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="30"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="27"/>
-    </row>
-    <row r="8" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="30"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="27"/>
-    </row>
-    <row r="9" spans="3:13" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="22"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="43" t="s">
+      <c r="G9" s="70"/>
+      <c r="H9" s="70"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="73" t="s">
+        <v>51</v>
+      </c>
+      <c r="L9" s="29"/>
+    </row>
+    <row r="10" spans="3:13" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="80"/>
+      <c r="D10" s="70"/>
+      <c r="E10" s="71" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="26" t="s">
+      <c r="G10" s="70"/>
+      <c r="H10" s="70"/>
+      <c r="I10" s="70"/>
+      <c r="J10" s="74"/>
+      <c r="K10" s="74"/>
+      <c r="L10" s="19"/>
+    </row>
+    <row r="11" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="18"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="70"/>
+      <c r="F11" s="70"/>
+      <c r="G11" s="70"/>
+      <c r="H11" s="70"/>
+      <c r="I11" s="70"/>
+      <c r="J11" s="74"/>
+      <c r="K11" s="74"/>
+      <c r="L11" s="19"/>
+    </row>
+    <row r="12" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="18"/>
+      <c r="D12" s="70"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="74"/>
+      <c r="K12" s="74"/>
+      <c r="L12" s="19"/>
+    </row>
+    <row r="13" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="81"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="70"/>
+      <c r="F13" s="70"/>
+      <c r="G13" s="70"/>
+      <c r="H13" s="70"/>
+      <c r="I13" s="70"/>
+      <c r="J13" s="70"/>
+      <c r="K13" s="70"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C14" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="43" t="s">
+        <v>4</v>
+      </c>
+      <c r="J14" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="46"/>
+      <c r="L14" s="47"/>
+    </row>
+    <row r="15" spans="3:13" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="36"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="44"/>
+      <c r="J15" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="L15" s="15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="3:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="3:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="13"/>
+      <c r="I22" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K22" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K23" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K24" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K26" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="23"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K27" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
+      <c r="G28" s="23"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K28" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K29" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C30" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
+      <c r="G30" s="23"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J30" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="K30" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="N30" s="21"/>
+    </row>
+    <row r="31" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="8"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="77"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+      <c r="I31" s="76"/>
+      <c r="J31" s="76"/>
+      <c r="K31" s="78"/>
+      <c r="L31" s="7"/>
+    </row>
+    <row r="32" spans="3:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="8"/>
+      <c r="D32" s="76"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="76"/>
+      <c r="J32" s="76"/>
+      <c r="K32" s="78"/>
+      <c r="L32" s="7"/>
+    </row>
+    <row r="33" spans="3:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="83"/>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="75"/>
+      <c r="L33" s="6"/>
+    </row>
+    <row r="34" spans="3:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="33"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="75"/>
+      <c r="K34" s="75"/>
+      <c r="L34" s="6"/>
+    </row>
+    <row r="35" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="84" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="85"/>
+      <c r="E35" s="85"/>
+      <c r="F35" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="50"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="75"/>
+      <c r="K35" s="75"/>
+      <c r="L35" s="6"/>
+    </row>
+    <row r="36" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="K9" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="L9" s="45"/>
-    </row>
-    <row r="10" spans="3:13" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="23"/>
-    </row>
-    <row r="11" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="22"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="23"/>
-    </row>
-    <row r="12" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="22"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="23"/>
-    </row>
-    <row r="13" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="22"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="107" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="109" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="110"/>
-      <c r="F14" s="110"/>
-      <c r="G14" s="110"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="115" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="75" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="76"/>
-      <c r="L14" s="77"/>
-    </row>
-    <row r="15" spans="3:13" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="108"/>
-      <c r="D15" s="112"/>
-      <c r="E15" s="113"/>
-      <c r="F15" s="113"/>
-      <c r="G15" s="113"/>
-      <c r="H15" s="114"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="L15" s="19" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="3:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C16" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K16" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="3:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L18" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L19" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L20" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L21" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J22" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K22" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L22" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J23" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L23" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="24" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J24" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L24" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="25" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E25" s="33"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L25" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="26" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26" s="33"/>
-      <c r="F26" s="33"/>
-      <c r="G26" s="33"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L26" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="27" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="28" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J28" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C29" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E29" s="33"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J29" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C30" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="N30" s="31"/>
-    </row>
-    <row r="31" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C31" s="12"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="9"/>
-    </row>
-    <row r="32" spans="3:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="12"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="9"/>
-    </row>
-    <row r="33" spans="3:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="88" t="s">
+      <c r="D36" s="85"/>
+      <c r="E36" s="85"/>
+      <c r="F36" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="48"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="48"/>
+      <c r="J36" s="48"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="49"/>
+    </row>
+    <row r="37" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="84"/>
+      <c r="D37" s="85"/>
+      <c r="E37" s="85"/>
+      <c r="F37" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
+      <c r="I37" s="51"/>
+      <c r="J37" s="51"/>
+      <c r="K37" s="51"/>
+      <c r="L37" s="52"/>
+    </row>
+    <row r="38" spans="3:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="53"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="54"/>
+      <c r="F38" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="D33" s="89"/>
-      <c r="E33" s="89"/>
-      <c r="F33" s="89"/>
-      <c r="G33" s="89"/>
-      <c r="H33" s="89"/>
-      <c r="I33" s="89"/>
-      <c r="L33" s="8"/>
-    </row>
-    <row r="34" spans="3:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="36"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="L34" s="8"/>
-    </row>
-    <row r="35" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D35" s="79"/>
-      <c r="E35" s="79"/>
-      <c r="F35" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="92"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="L35" s="8"/>
-    </row>
-    <row r="36" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="78" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="79"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="80" t="s">
-        <v>21</v>
-      </c>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="80"/>
-      <c r="J36" s="80"/>
-      <c r="K36" s="80"/>
-      <c r="L36" s="81"/>
-    </row>
-    <row r="37" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="78"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="93" t="s">
-        <v>22</v>
-      </c>
-      <c r="G37" s="93"/>
-      <c r="H37" s="93"/>
-      <c r="I37" s="93"/>
-      <c r="J37" s="93"/>
-      <c r="K37" s="93"/>
-      <c r="L37" s="94"/>
-    </row>
-    <row r="38" spans="3:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="95"/>
-      <c r="D38" s="96"/>
-      <c r="E38" s="96"/>
-      <c r="F38" s="100" t="s">
-        <v>45</v>
-      </c>
-      <c r="G38" s="100"/>
-      <c r="H38" s="100"/>
-      <c r="I38" s="100"/>
-      <c r="J38" s="100"/>
-      <c r="K38" s="100"/>
-      <c r="L38" s="101"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="56"/>
     </row>
     <row r="39" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="7"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="79"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
+      <c r="I39" s="77"/>
+      <c r="J39" s="77"/>
+      <c r="K39" s="77"/>
       <c r="L39" s="4"/>
     </row>
     <row r="40" spans="3:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C40" s="7"/>
-      <c r="D40" s="6"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="79"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
+      <c r="I40" s="77"/>
+      <c r="J40" s="77"/>
+      <c r="K40" s="77"/>
       <c r="L40" s="4"/>
       <c r="N40" s="3"/>
     </row>
     <row r="41" spans="3:14" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="90" t="s">
+      <c r="C41" s="115" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" s="115"/>
+      <c r="E41" s="115"/>
+      <c r="F41" s="115"/>
+      <c r="G41" s="115"/>
+      <c r="H41" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="D41" s="70"/>
-      <c r="E41" s="70"/>
-      <c r="F41" s="70"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="97" t="s">
+      <c r="I41" s="116"/>
+      <c r="J41" s="116"/>
+      <c r="K41" s="116"/>
+      <c r="L41" s="116"/>
+    </row>
+    <row r="42" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C42" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="98"/>
-      <c r="J41" s="98"/>
-      <c r="K41" s="98"/>
-      <c r="L41" s="99"/>
-    </row>
-    <row r="42" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C42" s="90" t="s">
+      <c r="D42" s="115"/>
+      <c r="E42" s="115"/>
+      <c r="F42" s="115"/>
+      <c r="G42" s="115"/>
+      <c r="H42" s="115" t="s">
         <v>25</v>
       </c>
-      <c r="D42" s="70"/>
-      <c r="E42" s="70"/>
-      <c r="F42" s="70"/>
-      <c r="G42" s="91"/>
-      <c r="H42" s="69" t="s">
-        <v>26</v>
-      </c>
-      <c r="I42" s="70"/>
-      <c r="J42" s="70"/>
-      <c r="K42" s="70"/>
-      <c r="L42" s="71"/>
-    </row>
-    <row r="43" spans="3:14" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C43" s="72" t="s">
+      <c r="I42" s="115"/>
+      <c r="J42" s="115"/>
+      <c r="K42" s="115"/>
+      <c r="L42" s="115"/>
+    </row>
+    <row r="43" spans="3:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C43" s="106" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="107"/>
+      <c r="E43" s="108"/>
+      <c r="F43" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="D43" s="73"/>
-      <c r="E43" s="74"/>
-      <c r="F43" s="72" t="s">
+      <c r="G43" s="108"/>
+      <c r="H43" s="106" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="108"/>
+      <c r="J43" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="K43" s="107"/>
+      <c r="L43" s="108"/>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="3:14" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C44" s="109" t="s">
+        <v>45</v>
+      </c>
+      <c r="D44" s="110"/>
+      <c r="E44" s="111"/>
+      <c r="F44" s="109" t="s">
         <v>33</v>
       </c>
-      <c r="G43" s="74"/>
-      <c r="H43" s="72" t="s">
-        <v>35</v>
-      </c>
-      <c r="I43" s="74"/>
-      <c r="J43" s="72" t="s">
+      <c r="G44" s="111"/>
+      <c r="H44" s="109" t="s">
         <v>36</v>
       </c>
-      <c r="K43" s="73"/>
-      <c r="L43" s="74"/>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="3:14" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="117" t="s">
+      <c r="I44" s="111"/>
+      <c r="J44" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="K44" s="110"/>
+      <c r="L44" s="111"/>
+    </row>
+    <row r="45" spans="3:14" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="98"/>
+      <c r="D45" s="99" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" s="100"/>
+      <c r="F45" s="101"/>
+      <c r="G45" s="97" t="s">
+        <v>47</v>
+      </c>
+      <c r="H45" s="102"/>
+      <c r="I45" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="D44" s="118"/>
-      <c r="E44" s="47" t="s">
+      <c r="J45" s="102"/>
+      <c r="K45" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="F44" s="48" t="s">
-        <v>34</v>
-      </c>
-      <c r="G44" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="H44" s="48" t="s">
-        <v>37</v>
-      </c>
-      <c r="I44" s="50" t="s">
+      <c r="L45" s="105"/>
+    </row>
+    <row r="46" spans="3:14" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="112" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" s="113"/>
+      <c r="E46" s="114"/>
+      <c r="F46" s="112" t="s">
+        <v>46</v>
+      </c>
+      <c r="G46" s="114"/>
+      <c r="H46" s="112" t="s">
+        <v>46</v>
+      </c>
+      <c r="I46" s="114"/>
+      <c r="J46" s="112" t="s">
+        <v>46</v>
+      </c>
+      <c r="K46" s="113"/>
+      <c r="L46" s="114"/>
+    </row>
+    <row r="47" spans="3:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C47" s="86" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="87"/>
+      <c r="E47" s="88"/>
+      <c r="F47" s="89" t="s">
+        <v>39</v>
+      </c>
+      <c r="G47" s="90"/>
+      <c r="H47" s="89" t="s">
+        <v>40</v>
+      </c>
+      <c r="I47" s="90"/>
+      <c r="J47" s="117" t="s">
         <v>52</v>
       </c>
-      <c r="J44" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="K44" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="L44" s="50"/>
-    </row>
-    <row r="45" spans="3:14" ht="24.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="82" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="87"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="82" t="s">
-        <v>50</v>
-      </c>
-      <c r="G45" s="83"/>
-      <c r="H45" s="82" t="s">
-        <v>50</v>
-      </c>
-      <c r="I45" s="83"/>
-      <c r="J45" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="K45" s="85"/>
-      <c r="L45" s="86"/>
-    </row>
-    <row r="46" spans="3:14" ht="24.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C46" s="102" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46" s="103"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="105" t="s">
-        <v>40</v>
-      </c>
-      <c r="G46" s="106"/>
-      <c r="H46" s="105" t="s">
-        <v>41</v>
-      </c>
-      <c r="I46" s="106"/>
-      <c r="J46" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="K46" s="39"/>
-      <c r="L46" s="42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-    </row>
-    <row r="48" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M49" s="1" t="s">
+      <c r="K47" s="118"/>
+      <c r="L47" s="119"/>
+    </row>
+    <row r="48" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="70"/>
+      <c r="D48" s="70"/>
+      <c r="E48" s="70"/>
+      <c r="F48" s="70"/>
+      <c r="G48" s="70"/>
+      <c r="H48" s="70"/>
+      <c r="I48" s="70"/>
+      <c r="J48" s="70"/>
+      <c r="K48" s="70"/>
+      <c r="L48" s="70"/>
+    </row>
+    <row r="49" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="75"/>
+      <c r="D49" s="75"/>
+      <c r="E49" s="75"/>
+      <c r="F49" s="75"/>
+      <c r="G49" s="75"/>
+      <c r="H49" s="75"/>
+      <c r="I49" s="75"/>
+      <c r="J49" s="75"/>
+      <c r="K49" s="75"/>
+      <c r="L49" s="75"/>
+    </row>
+    <row r="50" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M50" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="13:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="55" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="13:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="69" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="C44:D44"/>
+  <mergeCells count="39">
+    <mergeCell ref="J44:L44"/>
+    <mergeCell ref="J47:L47"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="E3:J6"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="D3:D6"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="C36:E37"/>
     <mergeCell ref="F36:L36"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="J45:L45"/>
-    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="C46:E46"/>
     <mergeCell ref="C33:I33"/>
     <mergeCell ref="C35:E35"/>
     <mergeCell ref="C42:G42"/>
@@ -2657,18 +2666,20 @@
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="H41:L41"/>
     <mergeCell ref="F38:L38"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:H15"/>
+    <mergeCell ref="I14:I15"/>
     <mergeCell ref="H42:L42"/>
     <mergeCell ref="C43:E43"/>
     <mergeCell ref="F43:G43"/>
     <mergeCell ref="H43:I43"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="E3:J6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F44:G44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>

--- a/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
+++ b/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SISTEMA-OFICIAL-AGARCORP\storage\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE540AF-840C-40F7-9C99-CFC96D4665E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689F25D7-FC4D-4190-B0C5-B9FE4FFE2700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
   </bookViews>

--- a/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
+++ b/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SISTEMA-OFICIAL-AGARCORP\storage\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{689F25D7-FC4D-4190-B0C5-B9FE4FFE2700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43198A9A-0165-4E10-8E0B-E7DF86FB94B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO SIN FORMULA" sheetId="2" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'FORMATO SIN FORMULA'!$C$3:$L$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'FORMATO SIN FORMULA'!$C$3:$M$49</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
     <author>Usuario</author>
   </authors>
   <commentList>
-    <comment ref="K9" authorId="0" shapeId="0" xr:uid="{D0CAA5AC-EF4E-4DF8-829F-3ED8C5F100A3}">
+    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{D0CAA5AC-EF4E-4DF8-829F-3ED8C5F100A3}">
       <text>
         <r>
           <rPr>
@@ -364,7 +364,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -421,9 +421,22 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <u/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -446,7 +459,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -511,28 +524,6 @@
     </border>
     <border>
       <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -946,105 +937,102 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -1052,110 +1040,8 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1186,9 +1072,102 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
     </xf>
@@ -1196,11 +1175,36 @@
       <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
@@ -1220,96 +1224,119 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1749,7 +1776,7 @@
   <sheetPr>
     <tabColor indexed="52"/>
   </sheetPr>
-  <dimension ref="C1:N75"/>
+  <dimension ref="B1:O75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
@@ -1757,211 +1784,225 @@
     <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23" style="1" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="24.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="21.109375" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.44140625" style="1"/>
+    <col min="6" max="6" width="10.21875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.21875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.109375" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:13" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="57"/>
-      <c r="D3" s="66"/>
-      <c r="E3" s="60" t="s">
+    <row r="1" spans="3:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:14" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="54"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
-      <c r="K3" s="91" t="s">
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="92"/>
-    </row>
-    <row r="4" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="58"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="93" t="s">
+      <c r="M3" s="64"/>
+    </row>
+    <row r="4" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="55"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="94"/>
-    </row>
-    <row r="5" spans="3:13" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="58"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="62"/>
-      <c r="F5" s="62"/>
-      <c r="G5" s="62"/>
-      <c r="H5" s="62"/>
-      <c r="I5" s="62"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="93"/>
-      <c r="L5" s="94"/>
-    </row>
-    <row r="6" spans="3:13" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="59"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="65"/>
-      <c r="K6" s="95" t="s">
+      <c r="M4" s="66"/>
+    </row>
+    <row r="5" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="55"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="66"/>
+    </row>
+    <row r="6" spans="3:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="56"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="62"/>
+      <c r="L6" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="L6" s="96"/>
-    </row>
-    <row r="7" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="31"/>
-      <c r="D7" s="69"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30"/>
-      <c r="K7" s="69"/>
-      <c r="L7" s="20"/>
-    </row>
-    <row r="8" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="32"/>
-      <c r="D8" s="69"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="69"/>
-      <c r="L8" s="20"/>
-    </row>
-    <row r="9" spans="3:13" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="68"/>
+    </row>
+    <row r="7" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="30"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="117"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="20"/>
+    </row>
+    <row r="8" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="31"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="29"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="20"/>
+    </row>
+    <row r="9" spans="3:14" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="18"/>
-      <c r="D9" s="70"/>
-      <c r="E9" s="71" t="s">
+      <c r="D9" s="36"/>
+      <c r="E9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="F9" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="70"/>
-      <c r="H9" s="70"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="72" t="s">
+      <c r="G9" s="119"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="K9" s="73" t="s">
+      <c r="L9" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="L9" s="29"/>
-    </row>
-    <row r="10" spans="3:13" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="80"/>
-      <c r="D10" s="70"/>
-      <c r="E10" s="71" t="s">
+      <c r="M9" s="28"/>
+    </row>
+    <row r="10" spans="3:14" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="46"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="120" t="s">
+      <c r="F10" s="118" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="70"/>
-      <c r="H10" s="70"/>
-      <c r="I10" s="70"/>
-      <c r="J10" s="74"/>
-      <c r="K10" s="74"/>
-      <c r="L10" s="19"/>
-    </row>
-    <row r="11" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="118"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="40"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="19"/>
+    </row>
+    <row r="11" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="18"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="70"/>
-      <c r="H11" s="70"/>
-      <c r="I11" s="70"/>
-      <c r="J11" s="74"/>
-      <c r="K11" s="74"/>
-      <c r="L11" s="19"/>
-    </row>
-    <row r="12" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="40"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="19"/>
+    </row>
+    <row r="12" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="18"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
-      <c r="F12" s="70"/>
-      <c r="G12" s="70"/>
-      <c r="H12" s="70"/>
-      <c r="I12" s="70"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="19"/>
-    </row>
-    <row r="13" spans="3:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="81"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="70"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="70"/>
-      <c r="I13" s="70"/>
-      <c r="J13" s="70"/>
-      <c r="K13" s="70"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C14" s="35" t="s">
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="19"/>
+    </row>
+    <row r="13" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="47"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="2"/>
+    </row>
+    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C14" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="97" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="38"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="43" t="s">
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="98"/>
+      <c r="I14" s="99"/>
+      <c r="J14" s="103" t="s">
         <v>4</v>
       </c>
-      <c r="J14" s="45" t="s">
+      <c r="K14" s="72" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="46"/>
-      <c r="L14" s="47"/>
-    </row>
-    <row r="15" spans="3:13" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="36"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="16" t="s">
+      <c r="L14" s="73"/>
+      <c r="M14" s="74"/>
+    </row>
+    <row r="15" spans="3:14" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="96"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="101"/>
+      <c r="F15" s="101"/>
+      <c r="G15" s="101"/>
+      <c r="H15" s="101"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="104"/>
+      <c r="K15" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="L15" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="L15" s="15" t="s">
+      <c r="M15" s="15" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="12" t="s">
         <v>26</v>
       </c>
@@ -1971,21 +2012,22 @@
       <c r="E16" s="23"/>
       <c r="F16" s="23"/>
       <c r="G16" s="23"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="25" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="K16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K16" s="10" t="s">
+      <c r="L16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="M16" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="3:14" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="12" t="s">
         <v>26</v>
       </c>
@@ -1995,21 +2037,22 @@
       <c r="E17" s="14"/>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="25" t="s">
+      <c r="H17" s="14"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="K17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="L17" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="M17" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="12" t="s">
         <v>26</v>
       </c>
@@ -2019,21 +2062,22 @@
       <c r="E18" s="14"/>
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="25" t="s">
+      <c r="H18" s="14"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J18" s="11" t="s">
+      <c r="K18" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="10" t="s">
+      <c r="L18" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="M18" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="12" t="s">
         <v>26</v>
       </c>
@@ -2043,21 +2087,22 @@
       <c r="E19" s="14"/>
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="25" t="s">
+      <c r="H19" s="14"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="K19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K19" s="10" t="s">
+      <c r="L19" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="M19" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2067,21 +2112,22 @@
       <c r="E20" s="14"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="25" t="s">
+      <c r="H20" s="14"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J20" s="11" t="s">
+      <c r="K20" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="10" t="s">
+      <c r="L20" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="M20" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="12" t="s">
         <v>26</v>
       </c>
@@ -2091,21 +2137,22 @@
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="25" t="s">
+      <c r="H21" s="14"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J21" s="11" t="s">
+      <c r="K21" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K21" s="10" t="s">
+      <c r="L21" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="M21" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="12" t="s">
         <v>26</v>
       </c>
@@ -2115,45 +2162,47 @@
       <c r="E22" s="14"/>
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="25" t="s">
+      <c r="H22" s="14"/>
+      <c r="I22" s="13"/>
+      <c r="J22" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J22" s="11" t="s">
+      <c r="K22" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K22" s="10" t="s">
+      <c r="L22" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="M22" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="12" t="s">
         <v>26</v>
       </c>
       <c r="D23" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="25" t="s">
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J23" s="11" t="s">
+      <c r="K23" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K23" s="10" t="s">
+      <c r="L23" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="M23" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="12" t="s">
         <v>26</v>
       </c>
@@ -2163,21 +2212,22 @@
       <c r="E24" s="26"/>
       <c r="F24" s="26"/>
       <c r="G24" s="26"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="25" t="s">
+      <c r="H24" s="26"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J24" s="11" t="s">
+      <c r="K24" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="10" t="s">
+      <c r="L24" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="M24" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="12" t="s">
         <v>26</v>
       </c>
@@ -2187,21 +2237,22 @@
       <c r="E25" s="23"/>
       <c r="F25" s="23"/>
       <c r="G25" s="23"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="25" t="s">
+      <c r="H25" s="23"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J25" s="11" t="s">
+      <c r="K25" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K25" s="10" t="s">
+      <c r="L25" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="M25" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="12" t="s">
         <v>26</v>
       </c>
@@ -2211,21 +2262,22 @@
       <c r="E26" s="23"/>
       <c r="F26" s="23"/>
       <c r="G26" s="23"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="25" t="s">
+      <c r="H26" s="23"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J26" s="11" t="s">
+      <c r="K26" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K26" s="10" t="s">
+      <c r="L26" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="M26" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="12" t="s">
         <v>26</v>
       </c>
@@ -2235,21 +2287,22 @@
       <c r="E27" s="23"/>
       <c r="F27" s="23"/>
       <c r="G27" s="23"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="25" t="s">
+      <c r="H27" s="23"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="K27" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K27" s="10" t="s">
+      <c r="L27" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="M27" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="12" t="s">
         <v>26</v>
       </c>
@@ -2259,21 +2312,22 @@
       <c r="E28" s="23"/>
       <c r="F28" s="23"/>
       <c r="G28" s="23"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="25" t="s">
+      <c r="H28" s="23"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="K28" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K28" s="10" t="s">
+      <c r="L28" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="M28" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="12" t="s">
         <v>26</v>
       </c>
@@ -2283,21 +2337,22 @@
       <c r="E29" s="23"/>
       <c r="F29" s="23"/>
       <c r="G29" s="23"/>
-      <c r="H29" s="24"/>
-      <c r="I29" s="25" t="s">
+      <c r="H29" s="23"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="K29" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K29" s="10" t="s">
+      <c r="L29" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L29" s="9" t="s">
+      <c r="M29" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="12" t="s">
         <v>26</v>
       </c>
@@ -2307,329 +2362,352 @@
       <c r="E30" s="23"/>
       <c r="F30" s="23"/>
       <c r="G30" s="23"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="25" t="s">
+      <c r="H30" s="23"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="J30" s="11" t="s">
+      <c r="K30" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="K30" s="10" t="s">
+      <c r="L30" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="M30" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="N30" s="21"/>
-    </row>
-    <row r="31" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O30" s="21"/>
+    </row>
+    <row r="31" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="8"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="76"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="7"/>
-    </row>
-    <row r="32" spans="3:14" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="42"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="7"/>
+    </row>
+    <row r="32" spans="3:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="8"/>
-      <c r="D32" s="76"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="76"/>
-      <c r="J32" s="76"/>
-      <c r="K32" s="78"/>
-      <c r="L32" s="7"/>
-    </row>
-    <row r="33" spans="3:14" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="82" t="s">
+      <c r="D32" s="42"/>
+      <c r="E32" s="43"/>
+      <c r="F32" s="43"/>
+      <c r="G32" s="43"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="7"/>
+    </row>
+    <row r="33" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="79" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="75"/>
-      <c r="L33" s="6"/>
-    </row>
-    <row r="34" spans="3:14" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="33"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="84" t="s">
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+      <c r="J33" s="80"/>
+      <c r="K33" s="41"/>
+      <c r="L33" s="41"/>
+      <c r="M33" s="6"/>
+    </row>
+    <row r="34" spans="2:15" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="32"/>
+      <c r="D34" s="33"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="41"/>
+      <c r="L34" s="41"/>
+      <c r="M34" s="6"/>
+    </row>
+    <row r="35" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="85"/>
-      <c r="E35" s="85"/>
-      <c r="F35" s="50" t="s">
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="82" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="50"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="75"/>
-      <c r="K35" s="75"/>
-      <c r="L35" s="6"/>
-    </row>
-    <row r="36" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="84" t="s">
+      <c r="G35" s="82"/>
+      <c r="H35" s="82"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="41"/>
+      <c r="L35" s="41"/>
+      <c r="M35" s="6"/>
+    </row>
+    <row r="36" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="85"/>
-      <c r="E36" s="85"/>
-      <c r="F36" s="48" t="s">
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
+      <c r="F36" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="48"/>
-      <c r="J36" s="48"/>
-      <c r="K36" s="48"/>
-      <c r="L36" s="49"/>
-    </row>
-    <row r="37" spans="3:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="84"/>
-      <c r="D37" s="85"/>
-      <c r="E37" s="85"/>
-      <c r="F37" s="51" t="s">
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="77"/>
+      <c r="K36" s="77"/>
+      <c r="L36" s="77"/>
+      <c r="M36" s="78"/>
+    </row>
+    <row r="37" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="75"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="76"/>
+      <c r="F37" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
-      <c r="I37" s="51"/>
-      <c r="J37" s="51"/>
-      <c r="K37" s="51"/>
-      <c r="L37" s="52"/>
-    </row>
-    <row r="38" spans="3:14" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="53"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="55" t="s">
+      <c r="G37" s="83"/>
+      <c r="H37" s="83"/>
+      <c r="I37" s="83"/>
+      <c r="J37" s="83"/>
+      <c r="K37" s="83"/>
+      <c r="L37" s="83"/>
+      <c r="M37" s="84"/>
+    </row>
+    <row r="38" spans="2:15" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="85"/>
+      <c r="D38" s="86"/>
+      <c r="E38" s="86"/>
+      <c r="F38" s="88" t="s">
         <v>43</v>
       </c>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="56"/>
-    </row>
-    <row r="39" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G38" s="88"/>
+      <c r="H38" s="88"/>
+      <c r="I38" s="88"/>
+      <c r="J38" s="88"/>
+      <c r="K38" s="88"/>
+      <c r="L38" s="88"/>
+      <c r="M38" s="89"/>
+    </row>
+    <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="5"/>
-      <c r="D39" s="79"/>
-      <c r="E39" s="70"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
-      <c r="J39" s="77"/>
-      <c r="K39" s="77"/>
-      <c r="L39" s="4"/>
-    </row>
-    <row r="40" spans="3:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="D39" s="45"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="43"/>
+      <c r="G39" s="43"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="43"/>
+      <c r="M39" s="4"/>
+    </row>
+    <row r="40" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C40" s="5"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="70"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="77"/>
-      <c r="K40" s="77"/>
-      <c r="L40" s="4"/>
-      <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="3:14" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="115" t="s">
+      <c r="D40" s="45"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="43"/>
+      <c r="G40" s="43"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="43"/>
+      <c r="M40" s="4"/>
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="115"/>
-      <c r="E41" s="115"/>
-      <c r="F41" s="115"/>
-      <c r="G41" s="115"/>
-      <c r="H41" s="116" t="s">
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="I41" s="116"/>
-      <c r="J41" s="116"/>
-      <c r="K41" s="116"/>
-      <c r="L41" s="116"/>
-    </row>
-    <row r="42" spans="3:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C42" s="115" t="s">
+      <c r="J41" s="87"/>
+      <c r="K41" s="87"/>
+      <c r="L41" s="87"/>
+      <c r="M41" s="87"/>
+    </row>
+    <row r="42" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C42" s="81" t="s">
         <v>24</v>
       </c>
-      <c r="D42" s="115"/>
-      <c r="E42" s="115"/>
-      <c r="F42" s="115"/>
-      <c r="G42" s="115"/>
-      <c r="H42" s="115" t="s">
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81" t="s">
         <v>25</v>
       </c>
-      <c r="I42" s="115"/>
-      <c r="J42" s="115"/>
-      <c r="K42" s="115"/>
-      <c r="L42" s="115"/>
-    </row>
-    <row r="43" spans="3:14" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C43" s="106" t="s">
+      <c r="J42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="81"/>
+      <c r="M42" s="81"/>
+    </row>
+    <row r="43" spans="2:15" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C43" s="105" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="107"/>
-      <c r="E43" s="108"/>
-      <c r="F43" s="106" t="s">
+      <c r="D43" s="106"/>
+      <c r="E43" s="107"/>
+      <c r="F43" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="G43" s="108"/>
-      <c r="H43" s="106" t="s">
+      <c r="G43" s="106"/>
+      <c r="H43" s="107"/>
+      <c r="I43" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="I43" s="108"/>
-      <c r="J43" s="106" t="s">
+      <c r="J43" s="107"/>
+      <c r="K43" s="105" t="s">
         <v>35</v>
       </c>
-      <c r="K43" s="107"/>
-      <c r="L43" s="108"/>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="3:14" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C44" s="109" t="s">
+      <c r="L43" s="106"/>
+      <c r="M43" s="107"/>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C44" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="110"/>
-      <c r="E44" s="111"/>
-      <c r="F44" s="109" t="s">
+      <c r="D44" s="49"/>
+      <c r="E44" s="50"/>
+      <c r="F44" s="48" t="s">
         <v>33</v>
       </c>
-      <c r="G44" s="111"/>
-      <c r="H44" s="109" t="s">
+      <c r="G44" s="49"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="48" t="s">
         <v>36</v>
       </c>
-      <c r="I44" s="111"/>
-      <c r="J44" s="109" t="s">
+      <c r="J44" s="50"/>
+      <c r="K44" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="K44" s="110"/>
-      <c r="L44" s="111"/>
-    </row>
-    <row r="45" spans="3:14" ht="3" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="98"/>
-      <c r="D45" s="99" t="s">
+      <c r="L44" s="49"/>
+      <c r="M44" s="50"/>
+    </row>
+    <row r="45" spans="2:15" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C45" s="111"/>
+      <c r="D45" s="123" t="s">
         <v>50</v>
       </c>
-      <c r="E45" s="100"/>
-      <c r="F45" s="101"/>
-      <c r="G45" s="97" t="s">
+      <c r="E45" s="124"/>
+      <c r="F45" s="120"/>
+      <c r="G45" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="H45" s="102"/>
-      <c r="I45" s="103" t="s">
+      <c r="H45" s="122"/>
+      <c r="I45" s="125"/>
+      <c r="J45" s="127" t="s">
         <v>48</v>
       </c>
-      <c r="J45" s="102"/>
-      <c r="K45" s="104" t="s">
+      <c r="K45" s="128"/>
+      <c r="L45" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="L45" s="105"/>
-    </row>
-    <row r="46" spans="3:14" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="112" t="s">
+      <c r="M45" s="112"/>
+    </row>
+    <row r="46" spans="2:15" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="108" t="s">
         <v>44</v>
       </c>
-      <c r="D46" s="113"/>
-      <c r="E46" s="114"/>
-      <c r="F46" s="112" t="s">
+      <c r="D46" s="109"/>
+      <c r="E46" s="110"/>
+      <c r="F46" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="G46" s="114"/>
-      <c r="H46" s="112" t="s">
+      <c r="G46" s="115"/>
+      <c r="H46" s="114"/>
+      <c r="I46" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="I46" s="114"/>
-      <c r="J46" s="112" t="s">
+      <c r="J46" s="129"/>
+      <c r="K46" s="130" t="s">
         <v>46</v>
       </c>
-      <c r="K46" s="113"/>
-      <c r="L46" s="114"/>
-    </row>
-    <row r="47" spans="3:14" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C47" s="86" t="s">
+      <c r="L46" s="131"/>
+      <c r="M46" s="132"/>
+    </row>
+    <row r="47" spans="2:15" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C47" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="87"/>
-      <c r="E47" s="88"/>
-      <c r="F47" s="89" t="s">
+      <c r="D47" s="91"/>
+      <c r="E47" s="92"/>
+      <c r="F47" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="G47" s="90"/>
-      <c r="H47" s="89" t="s">
+      <c r="G47" s="116"/>
+      <c r="H47" s="94"/>
+      <c r="I47" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="I47" s="90"/>
-      <c r="J47" s="117" t="s">
+      <c r="J47" s="94"/>
+      <c r="K47" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="K47" s="118"/>
-      <c r="L47" s="119"/>
-    </row>
-    <row r="48" spans="3:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C48" s="70"/>
-      <c r="D48" s="70"/>
-      <c r="E48" s="70"/>
-      <c r="F48" s="70"/>
-      <c r="G48" s="70"/>
-      <c r="H48" s="70"/>
-      <c r="I48" s="70"/>
-      <c r="J48" s="70"/>
-      <c r="K48" s="70"/>
-      <c r="L48" s="70"/>
-    </row>
-    <row r="49" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="75"/>
-      <c r="D49" s="75"/>
-      <c r="E49" s="75"/>
-      <c r="F49" s="75"/>
-      <c r="G49" s="75"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="75"/>
-      <c r="J49" s="75"/>
-      <c r="K49" s="75"/>
-      <c r="L49" s="75"/>
-    </row>
-    <row r="50" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M50" s="1" t="s">
+      <c r="L47" s="52"/>
+      <c r="M47" s="53"/>
+    </row>
+    <row r="48" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B48" s="21"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="36"/>
+      <c r="M48" s="36"/>
+    </row>
+    <row r="49" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="41"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
+      <c r="H49" s="41"/>
+      <c r="I49" s="41"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="41"/>
+      <c r="M49" s="41"/>
+    </row>
+    <row r="50" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N50" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="3:13" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="3:13" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="51" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H52" s="21"/>
+    </row>
+    <row r="56" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2640,46 +2718,44 @@
     <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J47:L47"/>
+  <mergeCells count="37">
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="I42:M42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="I41:M41"/>
+    <mergeCell ref="F38:M38"/>
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="K47:M47"/>
     <mergeCell ref="C3:C6"/>
-    <mergeCell ref="E3:J6"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="E3:K6"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="L6:M6"/>
     <mergeCell ref="D3:D6"/>
-    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="K14:M14"/>
     <mergeCell ref="C36:E37"/>
-    <mergeCell ref="F36:L36"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="J46:L46"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="K46:M46"/>
     <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F37:L37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="H41:L41"/>
-    <mergeCell ref="F38:L38"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="H42:L42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="J43:L43"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="F44:G44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>

--- a/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
+++ b/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SISTEMA-OFICIAL-AGARCORP\storage\app\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43198A9A-0165-4E10-8E0B-E7DF86FB94B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35CCAA5-D3C8-4F5B-8AF8-4D47EA6205E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO SIN FORMULA" sheetId="2" r:id="rId1"/>
@@ -1074,221 +1074,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1318,16 +1117,201 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
@@ -1337,6 +1321,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1363,15 +1363,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>106680</xdr:colOff>
+          <xdr:colOff>104775</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>137160</xdr:rowOff>
+          <xdr:rowOff>133350</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>480060</xdr:colOff>
+          <xdr:colOff>476250</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>137160</xdr:rowOff>
+          <xdr:rowOff>133350</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1477,9 +1477,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1517,7 +1517,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1623,7 +1623,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1765,7 +1765,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1777,88 +1777,88 @@
     <tabColor indexed="52"/>
   </sheetPr>
   <dimension ref="B1:O75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.88671875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.21875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.6640625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.109375" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.44140625" style="1"/>
+    <col min="8" max="8" width="16.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.85546875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.140625" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:14" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="54"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="57" t="s">
+    <row r="1" spans="3:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="3:14" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="102"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="63" t="s">
+      <c r="F3" s="105"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+      <c r="K3" s="106"/>
+      <c r="L3" s="111" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="64"/>
-    </row>
-    <row r="4" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="55"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="59"/>
-      <c r="I4" s="59"/>
-      <c r="J4" s="59"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="65" t="s">
+      <c r="M3" s="112"/>
+    </row>
+    <row r="4" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C4" s="103"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="107"/>
+      <c r="F4" s="107"/>
+      <c r="G4" s="107"/>
+      <c r="H4" s="107"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="108"/>
+      <c r="L4" s="113" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="66"/>
-    </row>
-    <row r="5" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="55"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="66"/>
-    </row>
-    <row r="6" spans="3:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C6" s="56"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
-      <c r="I6" s="61"/>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
-      <c r="L6" s="67" t="s">
+      <c r="M4" s="114"/>
+    </row>
+    <row r="5" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C5" s="103"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="107"/>
+      <c r="G5" s="107"/>
+      <c r="H5" s="107"/>
+      <c r="I5" s="107"/>
+      <c r="J5" s="107"/>
+      <c r="K5" s="108"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="114"/>
+    </row>
+    <row r="6" spans="3:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="104"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="115" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="68"/>
-    </row>
-    <row r="7" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M6" s="116"/>
+    </row>
+    <row r="7" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="30"/>
       <c r="D7" s="35"/>
       <c r="E7" s="29"/>
@@ -1866,12 +1866,12 @@
       <c r="G7" s="34"/>
       <c r="H7" s="29"/>
       <c r="I7" s="29"/>
-      <c r="J7" s="117"/>
+      <c r="J7" s="53"/>
       <c r="K7" s="29"/>
       <c r="L7" s="35"/>
       <c r="M7" s="20"/>
     </row>
-    <row r="8" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="31"/>
       <c r="D8" s="35"/>
       <c r="E8" s="29"/>
@@ -1884,16 +1884,16 @@
       <c r="L8" s="35"/>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" spans="3:14" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:14" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C9" s="18"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="119" t="s">
+      <c r="F9" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="119"/>
+      <c r="G9" s="55"/>
       <c r="H9" s="36"/>
       <c r="I9" s="36"/>
       <c r="J9" s="36"/>
@@ -1905,16 +1905,16 @@
       </c>
       <c r="M9" s="28"/>
     </row>
-    <row r="10" spans="3:14" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:14" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C10" s="46"/>
       <c r="D10" s="36"/>
       <c r="E10" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="118" t="s">
+      <c r="F10" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="118"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="36"/>
       <c r="I10" s="36"/>
       <c r="J10" s="36"/>
@@ -1922,7 +1922,7 @@
       <c r="L10" s="40"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="18"/>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -1935,7 +1935,7 @@
       <c r="L11" s="40"/>
       <c r="M11" s="19"/>
     </row>
-    <row r="12" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="18"/>
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
@@ -1948,7 +1948,7 @@
       <c r="L12" s="40"/>
       <c r="M12" s="19"/>
     </row>
-    <row r="13" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="47"/>
       <c r="D13" s="36"/>
       <c r="E13" s="36"/>
@@ -1962,36 +1962,36 @@
       <c r="M13" s="17"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
-      <c r="C14" s="95" t="s">
+    <row r="14" spans="3:14" x14ac:dyDescent="0.25">
+      <c r="C14" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="97" t="s">
+      <c r="D14" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="98"/>
-      <c r="F14" s="98"/>
-      <c r="G14" s="98"/>
-      <c r="H14" s="98"/>
-      <c r="I14" s="99"/>
-      <c r="J14" s="103" t="s">
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="74"/>
+      <c r="J14" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="72" t="s">
+      <c r="K14" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="73"/>
-      <c r="M14" s="74"/>
-    </row>
-    <row r="15" spans="3:14" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="96"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="102"/>
-      <c r="J15" s="104"/>
+      <c r="L14" s="121"/>
+      <c r="M14" s="122"/>
+    </row>
+    <row r="15" spans="3:14" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="71"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="76"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="79"/>
       <c r="K15" s="16" t="s">
         <v>7</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="12" t="s">
         <v>26</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="3:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="12" t="s">
         <v>26</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="12" t="s">
         <v>26</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="12" t="s">
         <v>26</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="12" t="s">
         <v>26</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="12" t="s">
         <v>26</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="12" t="s">
         <v>26</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="12" t="s">
         <v>26</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="12" t="s">
         <v>26</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="12" t="s">
         <v>26</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="12" t="s">
         <v>26</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="12" t="s">
         <v>26</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="12" t="s">
         <v>26</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="12" t="s">
         <v>26</v>
       </c>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="O30" s="21"/>
     </row>
-    <row r="31" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="8"/>
       <c r="D31" s="42"/>
       <c r="E31" s="43"/>
@@ -2391,7 +2391,7 @@
       <c r="L31" s="44"/>
       <c r="M31" s="7"/>
     </row>
-    <row r="32" spans="3:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="3:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="8"/>
       <c r="D32" s="42"/>
       <c r="E32" s="43"/>
@@ -2404,22 +2404,22 @@
       <c r="L32" s="44"/>
       <c r="M32" s="7"/>
     </row>
-    <row r="33" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C33" s="79" t="s">
+    <row r="33" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="87" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="80"/>
-      <c r="E33" s="80"/>
-      <c r="F33" s="80"/>
-      <c r="G33" s="80"/>
-      <c r="H33" s="80"/>
-      <c r="I33" s="80"/>
-      <c r="J33" s="80"/>
+      <c r="D33" s="88"/>
+      <c r="E33" s="88"/>
+      <c r="F33" s="88"/>
+      <c r="G33" s="88"/>
+      <c r="H33" s="88"/>
+      <c r="I33" s="88"/>
+      <c r="J33" s="88"/>
       <c r="K33" s="41"/>
       <c r="L33" s="41"/>
       <c r="M33" s="6"/>
     </row>
-    <row r="34" spans="2:15" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="32"/>
       <c r="D34" s="33"/>
       <c r="E34" s="33"/>
@@ -2432,71 +2432,71 @@
       <c r="L34" s="41"/>
       <c r="M34" s="6"/>
     </row>
-    <row r="35" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="75" t="s">
+    <row r="35" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="82" t="s">
+      <c r="D35" s="90"/>
+      <c r="E35" s="90"/>
+      <c r="F35" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="82"/>
-      <c r="H35" s="82"/>
+      <c r="G35" s="91"/>
+      <c r="H35" s="91"/>
       <c r="I35" s="33"/>
       <c r="J35" s="33"/>
       <c r="K35" s="41"/>
       <c r="L35" s="41"/>
       <c r="M35" s="6"/>
     </row>
-    <row r="36" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="75" t="s">
+    <row r="36" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="89" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
-      <c r="F36" s="77" t="s">
+      <c r="D36" s="90"/>
+      <c r="E36" s="90"/>
+      <c r="F36" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="77"/>
-      <c r="K36" s="77"/>
-      <c r="L36" s="77"/>
-      <c r="M36" s="78"/>
-    </row>
-    <row r="37" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="75"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="76"/>
-      <c r="F37" s="83" t="s">
+      <c r="G36" s="123"/>
+      <c r="H36" s="123"/>
+      <c r="I36" s="123"/>
+      <c r="J36" s="123"/>
+      <c r="K36" s="123"/>
+      <c r="L36" s="123"/>
+      <c r="M36" s="124"/>
+    </row>
+    <row r="37" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="89"/>
+      <c r="D37" s="90"/>
+      <c r="E37" s="90"/>
+      <c r="F37" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="84"/>
-    </row>
-    <row r="38" spans="2:15" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C38" s="85"/>
-      <c r="D38" s="86"/>
-      <c r="E38" s="86"/>
-      <c r="F38" s="88" t="s">
+      <c r="G37" s="92"/>
+      <c r="H37" s="92"/>
+      <c r="I37" s="92"/>
+      <c r="J37" s="92"/>
+      <c r="K37" s="92"/>
+      <c r="L37" s="92"/>
+      <c r="M37" s="93"/>
+    </row>
+    <row r="38" spans="2:15" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="94"/>
+      <c r="D38" s="95"/>
+      <c r="E38" s="95"/>
+      <c r="F38" s="97" t="s">
         <v>43</v>
       </c>
-      <c r="G38" s="88"/>
-      <c r="H38" s="88"/>
-      <c r="I38" s="88"/>
-      <c r="J38" s="88"/>
-      <c r="K38" s="88"/>
-      <c r="L38" s="88"/>
-      <c r="M38" s="89"/>
-    </row>
-    <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G38" s="97"/>
+      <c r="H38" s="97"/>
+      <c r="I38" s="97"/>
+      <c r="J38" s="97"/>
+      <c r="K38" s="97"/>
+      <c r="L38" s="97"/>
+      <c r="M38" s="98"/>
+    </row>
+    <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="5"/>
       <c r="D39" s="45"/>
       <c r="E39" s="36"/>
@@ -2509,7 +2509,7 @@
       <c r="L39" s="43"/>
       <c r="M39" s="4"/>
     </row>
-    <row r="40" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C40" s="5"/>
       <c r="D40" s="45"/>
       <c r="E40" s="36"/>
@@ -2523,147 +2523,147 @@
       <c r="M40" s="4"/>
       <c r="O40" s="3"/>
     </row>
-    <row r="41" spans="2:15" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="81" t="s">
+    <row r="41" spans="2:15" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="80" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="81"/>
-      <c r="E41" s="81"/>
-      <c r="F41" s="81"/>
-      <c r="G41" s="81"/>
-      <c r="H41" s="81"/>
-      <c r="I41" s="87" t="s">
+      <c r="D41" s="80"/>
+      <c r="E41" s="80"/>
+      <c r="F41" s="80"/>
+      <c r="G41" s="80"/>
+      <c r="H41" s="80"/>
+      <c r="I41" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="J41" s="87"/>
-      <c r="K41" s="87"/>
-      <c r="L41" s="87"/>
-      <c r="M41" s="87"/>
-    </row>
-    <row r="42" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C42" s="81" t="s">
+      <c r="J41" s="96"/>
+      <c r="K41" s="96"/>
+      <c r="L41" s="96"/>
+      <c r="M41" s="96"/>
+    </row>
+    <row r="42" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="80" t="s">
         <v>24</v>
       </c>
-      <c r="D42" s="81"/>
-      <c r="E42" s="81"/>
-      <c r="F42" s="81"/>
-      <c r="G42" s="81"/>
-      <c r="H42" s="81"/>
-      <c r="I42" s="81" t="s">
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="80"/>
+      <c r="I42" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="J42" s="81"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="81"/>
-      <c r="M42" s="81"/>
-    </row>
-    <row r="43" spans="2:15" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C43" s="105" t="s">
+      <c r="J42" s="80"/>
+      <c r="K42" s="80"/>
+      <c r="L42" s="80"/>
+      <c r="M42" s="80"/>
+    </row>
+    <row r="43" spans="2:15" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C43" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="106"/>
-      <c r="E43" s="107"/>
-      <c r="F43" s="105" t="s">
+      <c r="D43" s="82"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="G43" s="106"/>
-      <c r="H43" s="107"/>
-      <c r="I43" s="105" t="s">
+      <c r="G43" s="82"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="J43" s="107"/>
-      <c r="K43" s="105" t="s">
+      <c r="J43" s="83"/>
+      <c r="K43" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="L43" s="106"/>
-      <c r="M43" s="107"/>
+      <c r="L43" s="82"/>
+      <c r="M43" s="83"/>
       <c r="O43" s="3"/>
     </row>
-    <row r="44" spans="2:15" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C44" s="48" t="s">
+    <row r="44" spans="2:15" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="84" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="49"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="48" t="s">
+      <c r="D44" s="86"/>
+      <c r="E44" s="85"/>
+      <c r="F44" s="84" t="s">
         <v>33</v>
       </c>
-      <c r="G44" s="49"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="48" t="s">
+      <c r="G44" s="86"/>
+      <c r="H44" s="85"/>
+      <c r="I44" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="50"/>
-      <c r="K44" s="48" t="s">
+      <c r="J44" s="85"/>
+      <c r="K44" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="L44" s="49"/>
-      <c r="M44" s="50"/>
-    </row>
-    <row r="45" spans="2:15" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C45" s="111"/>
-      <c r="D45" s="123" t="s">
+      <c r="L44" s="86"/>
+      <c r="M44" s="85"/>
+    </row>
+    <row r="45" spans="2:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="48"/>
+      <c r="D45" s="59" t="s">
         <v>50</v>
       </c>
-      <c r="E45" s="124"/>
-      <c r="F45" s="120"/>
-      <c r="G45" s="121" t="s">
+      <c r="E45" s="60"/>
+      <c r="F45" s="56"/>
+      <c r="G45" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="H45" s="122"/>
-      <c r="I45" s="125"/>
-      <c r="J45" s="127" t="s">
+      <c r="H45" s="58"/>
+      <c r="I45" s="61"/>
+      <c r="J45" s="132" t="s">
         <v>48</v>
       </c>
-      <c r="K45" s="128"/>
-      <c r="L45" s="126" t="s">
+      <c r="K45" s="63"/>
+      <c r="L45" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="M45" s="112"/>
-    </row>
-    <row r="46" spans="2:15" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C46" s="108" t="s">
+      <c r="M45" s="49"/>
+    </row>
+    <row r="46" spans="2:15" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="128" t="s">
         <v>44</v>
       </c>
-      <c r="D46" s="109"/>
-      <c r="E46" s="110"/>
-      <c r="F46" s="113" t="s">
+      <c r="D46" s="129"/>
+      <c r="E46" s="130"/>
+      <c r="F46" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="G46" s="115"/>
-      <c r="H46" s="114"/>
-      <c r="I46" s="113" t="s">
+      <c r="G46" s="52"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="J46" s="129"/>
-      <c r="K46" s="130" t="s">
+      <c r="J46" s="131"/>
+      <c r="K46" s="125" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="131"/>
-      <c r="M46" s="132"/>
-    </row>
-    <row r="47" spans="2:15" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C47" s="90" t="s">
+      <c r="L46" s="126"/>
+      <c r="M46" s="127"/>
+    </row>
+    <row r="47" spans="2:15" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="91"/>
-      <c r="E47" s="92"/>
-      <c r="F47" s="93" t="s">
+      <c r="D47" s="65"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="67" t="s">
         <v>39</v>
       </c>
-      <c r="G47" s="116"/>
-      <c r="H47" s="94"/>
-      <c r="I47" s="93" t="s">
+      <c r="G47" s="68"/>
+      <c r="H47" s="69"/>
+      <c r="I47" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="J47" s="94"/>
-      <c r="K47" s="51" t="s">
+      <c r="J47" s="69"/>
+      <c r="K47" s="99" t="s">
         <v>52</v>
       </c>
-      <c r="L47" s="52"/>
-      <c r="M47" s="53"/>
-    </row>
-    <row r="48" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L47" s="100"/>
+      <c r="M47" s="101"/>
+    </row>
+    <row r="48" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="21"/>
       <c r="C48" s="36"/>
       <c r="D48" s="36"/>
@@ -2677,7 +2677,7 @@
       <c r="L48" s="36"/>
       <c r="M48" s="36"/>
     </row>
-    <row r="49" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="41"/>
       <c r="D49" s="41"/>
       <c r="E49" s="41"/>
@@ -2690,35 +2690,56 @@
       <c r="L49" s="41"/>
       <c r="M49" s="41"/>
     </row>
-    <row r="50" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="N50" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H52" s="21"/>
     </row>
-    <row r="56" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="57" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="58" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="59" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="60" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="61" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="62" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="63" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="64" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="68" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="70" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="K44:M44"/>
+    <mergeCell ref="K47:M47"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="E3:K6"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="C36:E37"/>
+    <mergeCell ref="F36:M36"/>
+    <mergeCell ref="K46:M46"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C42:H42"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="I41:M41"/>
+    <mergeCell ref="F38:M38"/>
     <mergeCell ref="C47:E47"/>
     <mergeCell ref="F47:H47"/>
     <mergeCell ref="I47:J47"/>
@@ -2735,27 +2756,6 @@
     <mergeCell ref="F44:H44"/>
     <mergeCell ref="C33:J33"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C42:H42"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="I41:M41"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="K44:M44"/>
-    <mergeCell ref="K47:M47"/>
-    <mergeCell ref="C3:C6"/>
-    <mergeCell ref="E3:K6"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="L5:M5"/>
-    <mergeCell ref="L6:M6"/>
-    <mergeCell ref="D3:D6"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="C36:E37"/>
-    <mergeCell ref="F36:M36"/>
-    <mergeCell ref="K46:M46"/>
-    <mergeCell ref="C46:E46"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
@@ -2771,15 +2771,15 @@
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>106680</xdr:colOff>
+                <xdr:colOff>104775</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>137160</xdr:rowOff>
+                <xdr:rowOff>133350</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>480060</xdr:colOff>
+                <xdr:colOff>476250</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>137160</xdr:rowOff>
+                <xdr:rowOff>133350</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -2796,7 +2796,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF103C6C-43B0-44D4-BD77-E1E3ABD37B7E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
+++ b/storage/app/templates/PLANILLA DE FORMATO DE COMPRA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\SISTEMA-OFICIAL-AGARCORP\storage\app\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\AppData\Roaming\MobaXterm\slash\RemoteFiles\66904_6_10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35CCAA5-D3C8-4F5B-8AF8-4D47EA6205E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75979803-B8F5-4CBF-A7FF-8D7BFD3B9A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3208A746-A803-4595-8525-051ED833FA61}"/>
   </bookViews>
   <sheets>
     <sheet name="FORMATO SIN FORMULA" sheetId="2" r:id="rId1"/>
@@ -1121,6 +1121,155 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" wrapText="1" indent="1"/>
       <protection locked="0"/>
@@ -1172,9 +1321,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1184,158 +1330,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1363,15 +1363,15 @@
       <xdr:twoCellAnchor>
         <xdr:from>
           <xdr:col>2</xdr:col>
-          <xdr:colOff>104775</xdr:colOff>
+          <xdr:colOff>106680</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>133350</xdr:rowOff>
+          <xdr:rowOff>137160</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>4</xdr:col>
-          <xdr:colOff>476250</xdr:colOff>
+          <xdr:colOff>480060</xdr:colOff>
           <xdr:row>26</xdr:row>
-          <xdr:rowOff>133350</xdr:rowOff>
+          <xdr:rowOff>137160</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1415,13 +1415,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>160400</xdr:colOff>
+      <xdr:colOff>258374</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>185054</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>1011313</xdr:colOff>
+      <xdr:colOff>1109287</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>104499</xdr:rowOff>
     </xdr:to>
@@ -1453,7 +1453,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2522600" y="838197"/>
+          <a:off x="2620574" y="838197"/>
           <a:ext cx="850913" cy="692331"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1477,9 +1477,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1517,7 +1517,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1623,7 +1623,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1765,7 +1765,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1777,88 +1777,88 @@
     <tabColor indexed="52"/>
   </sheetPr>
   <dimension ref="B1:O75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="10" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.85546875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" style="1" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="21.140625" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.42578125" style="1"/>
+    <col min="8" max="8" width="16.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="14.109375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="21.109375" style="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="3:14" ht="18.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="102"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="105" t="s">
+    <row r="1" spans="3:14" ht="33.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:14" ht="18" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="72"/>
+      <c r="D3" s="87"/>
+      <c r="E3" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="105"/>
-      <c r="G3" s="105"/>
-      <c r="H3" s="105"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="105"/>
-      <c r="K3" s="106"/>
-      <c r="L3" s="111" t="s">
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
+      <c r="J3" s="75"/>
+      <c r="K3" s="76"/>
+      <c r="L3" s="81" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="112"/>
-    </row>
-    <row r="4" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="103"/>
-      <c r="D4" s="118"/>
-      <c r="E4" s="107"/>
-      <c r="F4" s="107"/>
-      <c r="G4" s="107"/>
-      <c r="H4" s="107"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="108"/>
-      <c r="L4" s="113" t="s">
+      <c r="M3" s="82"/>
+    </row>
+    <row r="4" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="73"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="83" t="s">
         <v>14</v>
       </c>
-      <c r="M4" s="114"/>
-    </row>
-    <row r="5" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C5" s="103"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="107"/>
-      <c r="G5" s="107"/>
-      <c r="H5" s="107"/>
-      <c r="I5" s="107"/>
-      <c r="J5" s="107"/>
-      <c r="K5" s="108"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="114"/>
-    </row>
-    <row r="6" spans="3:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="104"/>
-      <c r="D6" s="119"/>
-      <c r="E6" s="109"/>
-      <c r="F6" s="109"/>
-      <c r="G6" s="109"/>
-      <c r="H6" s="109"/>
-      <c r="I6" s="109"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="115" t="s">
+      <c r="M4" s="84"/>
+    </row>
+    <row r="5" spans="3:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="73"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="77"/>
+      <c r="G5" s="77"/>
+      <c r="H5" s="77"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="78"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="84"/>
+    </row>
+    <row r="6" spans="3:14" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="74"/>
+      <c r="D6" s="89"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
+      <c r="G6" s="79"/>
+      <c r="H6" s="79"/>
+      <c r="I6" s="79"/>
+      <c r="J6" s="79"/>
+      <c r="K6" s="80"/>
+      <c r="L6" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="116"/>
-    </row>
-    <row r="7" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M6" s="86"/>
+    </row>
+    <row r="7" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="30"/>
       <c r="D7" s="35"/>
       <c r="E7" s="29"/>
@@ -1871,7 +1871,7 @@
       <c r="L7" s="35"/>
       <c r="M7" s="20"/>
     </row>
-    <row r="8" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="31"/>
       <c r="D8" s="35"/>
       <c r="E8" s="29"/>
@@ -1884,7 +1884,7 @@
       <c r="L8" s="35"/>
       <c r="M8" s="20"/>
     </row>
-    <row r="9" spans="3:14" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:14" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="18"/>
       <c r="D9" s="36"/>
       <c r="E9" s="37" t="s">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="M9" s="28"/>
     </row>
-    <row r="10" spans="3:14" ht="23.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:14" ht="23.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="46"/>
       <c r="D10" s="36"/>
       <c r="E10" s="37" t="s">
@@ -1922,7 +1922,7 @@
       <c r="L10" s="40"/>
       <c r="M10" s="19"/>
     </row>
-    <row r="11" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="18"/>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -1935,7 +1935,7 @@
       <c r="L11" s="40"/>
       <c r="M11" s="19"/>
     </row>
-    <row r="12" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="18"/>
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
@@ -1948,7 +1948,7 @@
       <c r="L12" s="40"/>
       <c r="M12" s="19"/>
     </row>
-    <row r="13" spans="3:14" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="47"/>
       <c r="D13" s="36"/>
       <c r="E13" s="36"/>
@@ -1962,36 +1962,36 @@
       <c r="M13" s="17"/>
       <c r="N13" s="2"/>
     </row>
-    <row r="14" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C14" s="70" t="s">
+    <row r="14" spans="3:14" x14ac:dyDescent="0.3">
+      <c r="C14" s="118" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="72" t="s">
+      <c r="D14" s="120" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="74"/>
-      <c r="J14" s="78" t="s">
+      <c r="E14" s="121"/>
+      <c r="F14" s="121"/>
+      <c r="G14" s="121"/>
+      <c r="H14" s="121"/>
+      <c r="I14" s="122"/>
+      <c r="J14" s="126" t="s">
         <v>4</v>
       </c>
-      <c r="K14" s="120" t="s">
+      <c r="K14" s="90" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="121"/>
-      <c r="M14" s="122"/>
-    </row>
-    <row r="15" spans="3:14" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="71"/>
-      <c r="D15" s="75"/>
-      <c r="E15" s="76"/>
-      <c r="F15" s="76"/>
-      <c r="G15" s="76"/>
-      <c r="H15" s="76"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="79"/>
+      <c r="L14" s="91"/>
+      <c r="M14" s="92"/>
+    </row>
+    <row r="15" spans="3:14" ht="17.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="119"/>
+      <c r="D15" s="123"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="127"/>
       <c r="K15" s="16" t="s">
         <v>7</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="12" t="s">
         <v>26</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="3:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="12" t="s">
         <v>26</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="12" t="s">
         <v>26</v>
       </c>
@@ -2077,7 +2077,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="12" t="s">
         <v>26</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2127,7 +2127,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="12" t="s">
         <v>26</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="12" t="s">
         <v>26</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="12" t="s">
         <v>26</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C24" s="12" t="s">
         <v>26</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="12" t="s">
         <v>26</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="12" t="s">
         <v>26</v>
       </c>
@@ -2277,7 +2277,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C27" s="12" t="s">
         <v>26</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="12" t="s">
         <v>26</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="12" t="s">
         <v>26</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="30" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="12" t="s">
         <v>26</v>
       </c>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="O30" s="21"/>
     </row>
-    <row r="31" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="8"/>
       <c r="D31" s="42"/>
       <c r="E31" s="43"/>
@@ -2391,7 +2391,7 @@
       <c r="L31" s="44"/>
       <c r="M31" s="7"/>
     </row>
-    <row r="32" spans="3:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="8"/>
       <c r="D32" s="42"/>
       <c r="E32" s="43"/>
@@ -2404,22 +2404,22 @@
       <c r="L32" s="44"/>
       <c r="M32" s="7"/>
     </row>
-    <row r="33" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C33" s="87" t="s">
+    <row r="33" spans="2:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="88"/>
-      <c r="E33" s="88"/>
-      <c r="F33" s="88"/>
-      <c r="G33" s="88"/>
-      <c r="H33" s="88"/>
-      <c r="I33" s="88"/>
-      <c r="J33" s="88"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="132"/>
+      <c r="F33" s="132"/>
+      <c r="G33" s="132"/>
+      <c r="H33" s="132"/>
+      <c r="I33" s="132"/>
+      <c r="J33" s="132"/>
       <c r="K33" s="41"/>
       <c r="L33" s="41"/>
       <c r="M33" s="6"/>
     </row>
-    <row r="34" spans="2:15" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:15" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="32"/>
       <c r="D34" s="33"/>
       <c r="E34" s="33"/>
@@ -2432,71 +2432,71 @@
       <c r="L34" s="41"/>
       <c r="M34" s="6"/>
     </row>
-    <row r="35" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C35" s="89" t="s">
+    <row r="35" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="D35" s="90"/>
-      <c r="E35" s="90"/>
-      <c r="F35" s="91" t="s">
+      <c r="D35" s="94"/>
+      <c r="E35" s="94"/>
+      <c r="F35" s="104" t="s">
         <v>19</v>
       </c>
-      <c r="G35" s="91"/>
-      <c r="H35" s="91"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="104"/>
       <c r="I35" s="33"/>
       <c r="J35" s="33"/>
       <c r="K35" s="41"/>
       <c r="L35" s="41"/>
       <c r="M35" s="6"/>
     </row>
-    <row r="36" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C36" s="89" t="s">
+    <row r="36" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="D36" s="90"/>
-      <c r="E36" s="90"/>
-      <c r="F36" s="123" t="s">
+      <c r="D36" s="94"/>
+      <c r="E36" s="94"/>
+      <c r="F36" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="G36" s="123"/>
-      <c r="H36" s="123"/>
-      <c r="I36" s="123"/>
-      <c r="J36" s="123"/>
-      <c r="K36" s="123"/>
-      <c r="L36" s="123"/>
-      <c r="M36" s="124"/>
-    </row>
-    <row r="37" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C37" s="89"/>
-      <c r="D37" s="90"/>
-      <c r="E37" s="90"/>
-      <c r="F37" s="92" t="s">
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="95"/>
+      <c r="J36" s="95"/>
+      <c r="K36" s="95"/>
+      <c r="L36" s="95"/>
+      <c r="M36" s="96"/>
+    </row>
+    <row r="37" spans="2:15" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="93"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
+      <c r="F37" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="G37" s="92"/>
-      <c r="H37" s="92"/>
-      <c r="I37" s="92"/>
-      <c r="J37" s="92"/>
-      <c r="K37" s="92"/>
-      <c r="L37" s="92"/>
-      <c r="M37" s="93"/>
-    </row>
-    <row r="38" spans="2:15" ht="34.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C38" s="94"/>
-      <c r="D38" s="95"/>
-      <c r="E38" s="95"/>
-      <c r="F38" s="97" t="s">
+      <c r="G37" s="105"/>
+      <c r="H37" s="105"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="105"/>
+      <c r="K37" s="105"/>
+      <c r="L37" s="105"/>
+      <c r="M37" s="106"/>
+    </row>
+    <row r="38" spans="2:15" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="107"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="110" t="s">
         <v>43</v>
       </c>
-      <c r="G38" s="97"/>
-      <c r="H38" s="97"/>
-      <c r="I38" s="97"/>
-      <c r="J38" s="97"/>
-      <c r="K38" s="97"/>
-      <c r="L38" s="97"/>
-      <c r="M38" s="98"/>
-    </row>
-    <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G38" s="110"/>
+      <c r="H38" s="110"/>
+      <c r="I38" s="110"/>
+      <c r="J38" s="110"/>
+      <c r="K38" s="110"/>
+      <c r="L38" s="110"/>
+      <c r="M38" s="111"/>
+    </row>
+    <row r="39" spans="2:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="5"/>
       <c r="D39" s="45"/>
       <c r="E39" s="36"/>
@@ -2509,7 +2509,7 @@
       <c r="L39" s="43"/>
       <c r="M39" s="4"/>
     </row>
-    <row r="40" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:15" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C40" s="5"/>
       <c r="D40" s="45"/>
       <c r="E40" s="36"/>
@@ -2523,84 +2523,84 @@
       <c r="M40" s="4"/>
       <c r="O40" s="3"/>
     </row>
-    <row r="41" spans="2:15" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="80" t="s">
+    <row r="41" spans="2:15" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="D41" s="80"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="80"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="80"/>
-      <c r="I41" s="96" t="s">
+      <c r="D41" s="103"/>
+      <c r="E41" s="103"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="103"/>
+      <c r="H41" s="103"/>
+      <c r="I41" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="96"/>
-    </row>
-    <row r="42" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C42" s="80" t="s">
+      <c r="J41" s="109"/>
+      <c r="K41" s="109"/>
+      <c r="L41" s="109"/>
+      <c r="M41" s="109"/>
+    </row>
+    <row r="42" spans="2:15" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C42" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="D42" s="80"/>
-      <c r="E42" s="80"/>
-      <c r="F42" s="80"/>
-      <c r="G42" s="80"/>
-      <c r="H42" s="80"/>
-      <c r="I42" s="80" t="s">
+      <c r="D42" s="103"/>
+      <c r="E42" s="103"/>
+      <c r="F42" s="103"/>
+      <c r="G42" s="103"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="103" t="s">
         <v>25</v>
       </c>
-      <c r="J42" s="80"/>
-      <c r="K42" s="80"/>
-      <c r="L42" s="80"/>
-      <c r="M42" s="80"/>
-    </row>
-    <row r="43" spans="2:15" ht="40.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C43" s="81" t="s">
+      <c r="J42" s="103"/>
+      <c r="K42" s="103"/>
+      <c r="L42" s="103"/>
+      <c r="M42" s="103"/>
+    </row>
+    <row r="43" spans="2:15" ht="40.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="C43" s="128" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="82"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="81" t="s">
+      <c r="D43" s="129"/>
+      <c r="E43" s="130"/>
+      <c r="F43" s="128" t="s">
         <v>32</v>
       </c>
-      <c r="G43" s="82"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="81" t="s">
+      <c r="G43" s="129"/>
+      <c r="H43" s="130"/>
+      <c r="I43" s="128" t="s">
         <v>34</v>
       </c>
-      <c r="J43" s="83"/>
-      <c r="K43" s="81" t="s">
+      <c r="J43" s="130"/>
+      <c r="K43" s="128" t="s">
         <v>35</v>
       </c>
-      <c r="L43" s="82"/>
-      <c r="M43" s="83"/>
+      <c r="L43" s="129"/>
+      <c r="M43" s="130"/>
       <c r="O43" s="3"/>
     </row>
-    <row r="44" spans="2:15" ht="25.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="84" t="s">
+    <row r="44" spans="2:15" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C44" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="D44" s="86"/>
-      <c r="E44" s="85"/>
-      <c r="F44" s="84" t="s">
+      <c r="D44" s="67"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="G44" s="86"/>
-      <c r="H44" s="85"/>
-      <c r="I44" s="84" t="s">
+      <c r="G44" s="67"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="J44" s="85"/>
-      <c r="K44" s="84" t="s">
+      <c r="J44" s="68"/>
+      <c r="K44" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="L44" s="86"/>
-      <c r="M44" s="85"/>
-    </row>
-    <row r="45" spans="2:15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L44" s="67"/>
+      <c r="M44" s="68"/>
+    </row>
+    <row r="45" spans="2:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="48"/>
       <c r="D45" s="59" t="s">
         <v>50</v>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="H45" s="58"/>
       <c r="I45" s="61"/>
-      <c r="J45" s="132" t="s">
+      <c r="J45" s="65" t="s">
         <v>48</v>
       </c>
       <c r="K45" s="63"/>
@@ -2621,12 +2621,12 @@
       </c>
       <c r="M45" s="49"/>
     </row>
-    <row r="46" spans="2:15" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C46" s="128" t="s">
+    <row r="46" spans="2:15" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="D46" s="129"/>
-      <c r="E46" s="130"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="102"/>
       <c r="F46" s="50" t="s">
         <v>46</v>
       </c>
@@ -2635,35 +2635,35 @@
       <c r="I46" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="J46" s="131"/>
-      <c r="K46" s="125" t="s">
+      <c r="J46" s="64"/>
+      <c r="K46" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="126"/>
-      <c r="M46" s="127"/>
-    </row>
-    <row r="47" spans="2:15" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C47" s="64" t="s">
+      <c r="L46" s="98"/>
+      <c r="M46" s="99"/>
+    </row>
+    <row r="47" spans="2:15" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C47" s="112" t="s">
         <v>38</v>
       </c>
-      <c r="D47" s="65"/>
-      <c r="E47" s="66"/>
-      <c r="F47" s="67" t="s">
+      <c r="D47" s="113"/>
+      <c r="E47" s="114"/>
+      <c r="F47" s="115" t="s">
         <v>39</v>
       </c>
-      <c r="G47" s="68"/>
-      <c r="H47" s="69"/>
-      <c r="I47" s="67" t="s">
+      <c r="G47" s="116"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="J47" s="69"/>
-      <c r="K47" s="99" t="s">
+      <c r="J47" s="117"/>
+      <c r="K47" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="L47" s="100"/>
-      <c r="M47" s="101"/>
-    </row>
-    <row r="48" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L47" s="70"/>
+      <c r="M47" s="71"/>
+    </row>
+    <row r="48" spans="2:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="21"/>
       <c r="C48" s="36"/>
       <c r="D48" s="36"/>
@@ -2677,7 +2677,7 @@
       <c r="L48" s="36"/>
       <c r="M48" s="36"/>
     </row>
-    <row r="49" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C49" s="41"/>
       <c r="D49" s="41"/>
       <c r="E49" s="41"/>
@@ -2690,35 +2690,56 @@
       <c r="L49" s="41"/>
       <c r="M49" s="41"/>
     </row>
-    <row r="50" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="N50" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:14" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="H52" s="21"/>
     </row>
-    <row r="56" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="57" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="58" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="59" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="60" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="61" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="62" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="63" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="64" spans="3:14" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="65" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="66" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="67" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="68" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="70" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="F47:H47"/>
+    <mergeCell ref="I47:J47"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="I42:M42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:M43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="C33:J33"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="F37:M37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="I41:M41"/>
+    <mergeCell ref="F38:M38"/>
     <mergeCell ref="K44:M44"/>
     <mergeCell ref="K47:M47"/>
     <mergeCell ref="C3:C6"/>
@@ -2735,27 +2756,6 @@
     <mergeCell ref="C46:E46"/>
     <mergeCell ref="C42:H42"/>
     <mergeCell ref="F35:H35"/>
-    <mergeCell ref="F37:M37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="I41:M41"/>
-    <mergeCell ref="F38:M38"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="F47:H47"/>
-    <mergeCell ref="I47:J47"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="I42:M42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:M43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="C33:J33"/>
-    <mergeCell ref="C35:E35"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094499" right="0.23622047244094499" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
@@ -2771,15 +2771,15 @@
             <anchor moveWithCells="1" sizeWithCells="1">
               <from>
                 <xdr:col>2</xdr:col>
-                <xdr:colOff>104775</xdr:colOff>
+                <xdr:colOff>106680</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
+                <xdr:rowOff>137160</xdr:rowOff>
               </from>
               <to>
                 <xdr:col>4</xdr:col>
-                <xdr:colOff>476250</xdr:colOff>
+                <xdr:colOff>480060</xdr:colOff>
                 <xdr:row>26</xdr:row>
-                <xdr:rowOff>133350</xdr:rowOff>
+                <xdr:rowOff>137160</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
@@ -2796,7 +2796,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF103C6C-43B0-44D4-BD77-E1E3ABD37B7E}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
